--- a/mistral_translate_work/split_by_prompt/excel/ui/lang_multi_text/lang_multi_text__ui__part_0014.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/ui/lang_multi_text/lang_multi_text__ui__part_0014.xlsx
@@ -576,7 +576,7 @@
       <c r="M2" t="inlineStr">
         <is>
           <t>Có vẻ như Black Shores đã đạt được bước đột phá trong Infinite Reality Sandbox, mang đến môi trường chân thực hơn và những trận chiến gay cấn hơn.
-Lần này, mô phỏng diễn ra tại Penitent's End, một hòn đảo hoang tàn nơi vô số linh hồn bị đày ải phải đón nhận số phận của mình.</t>
+Lần này, mô phỏng diễn ra tại Penitent's End, một hòn đảo hoang tàn nơi vô số linh hồn bị lưu đày phải đón nhận số phận của mình.</t>
         </is>
       </c>
     </row>
@@ -643,7 +643,7 @@
       <c r="M3" t="inlineStr">
         <is>
           <t>Có vẻ như Black Shores đã đạt được bước đột phá trong Infinite Reality Sandbox, mang đến môi trường chân thực hơn và những trận chiến gay cấn hơn.
-Lần này, mô phỏng diễn ra tại Penitent's End, một hòn đảo hoang tàn nơi vô số linh hồn bị đày ải phải đón nhận số phận của mình.</t>
+Lần này, mô phỏng diễn ra tại Penitent's End, một hòn đảo hoang tàn nơi vô số linh hồn bị lưu đày phải đón nhận số phận của mình.</t>
         </is>
       </c>
     </row>
@@ -710,7 +710,7 @@
       <c r="M4" t="inlineStr">
         <is>
           <t>Có vẻ như Black Shores đã đạt được bước đột phá trong Infinite Reality Sandbox, mang đến môi trường chân thực hơn và những trận chiến gay cấn hơn.
-Lần này, mô phỏng diễn ra tại Penitent's End, một hòn đảo hoang tàn nơi vô số linh hồn bị đày ải phải đón nhận số phận của mình.</t>
+Lần này, mô phỏng diễn ra tại Penitent's End, một hòn đảo hoang tàn nơi vô số linh hồn bị lưu đày phải đón nhận số phận của mình.</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
       <c r="M5" t="inlineStr">
         <is>
           <t>Có vẻ như Black Shores đã đạt được bước đột phá trong Infinite Reality Sandbox, mang đến môi trường chân thực hơn và những trận chiến gay cấn hơn.
-Lần này, mô phỏng diễn ra tại Penitent's End, một hòn đảo hoang tàn nơi vô số linh hồn bị đày ải phải đón nhận số phận của mình.</t>
+Lần này, mô phỏng diễn ra tại Penitent's End, một hòn đảo hoang tàn nơi vô số linh hồn bị lưu đày phải đón nhận số phận của mình.</t>
         </is>
       </c>
     </row>
@@ -844,7 +844,7 @@
       <c r="M6" t="inlineStr">
         <is>
           <t>Có vẻ như Black Shores đã đạt được bước đột phá trong Infinite Reality Sandbox, mang đến môi trường chân thực hơn và những trận chiến gay cấn hơn.
-Lần này, mô phỏng diễn ra tại Penitent's End, một hòn đảo hoang tàn nơi vô số linh hồn bị đày ải phải đón nhận số phận của mình.</t>
+Lần này, mô phỏng diễn ra tại Penitent's End, một hòn đảo hoang tàn nơi vô số linh hồn bị lưu đày phải đón nhận số phận của mình.</t>
         </is>
       </c>
     </row>
@@ -909,7 +909,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Một cánh cổng quen thuộc xuất hiện trên vùng đất Rinascita, kết nối với một thế giới gọi là Somnoire. Những ký ức xưa chôn giấu sâu trong giấc mơ, và chìa khóa khám phá nằm trong tay bạn. Xin đừng quên, chỉ trong giấc mơ mới tìm thấy câu trả lời.</t>
+          <t>Một cánh cổng quen thuộc xuất hiện trên vùng đất Rinascita, nối liền với thế giới mang tên Somnoire. Những ký ức xa xưa chôn sâu trong giấc mơ, và chìa khóa khám phá giờ nằm trong tay ngươi. Đừng quên, chỉ trong giấc mơ, câu trả lời mới được hé lộ.</t>
         </is>
       </c>
     </row>
@@ -974,7 +974,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Một cánh cổng quen thuộc xuất hiện trên vùng đất Rinascita, kết nối với một thế giới gọi là Somnoire. Những ký ức xưa chôn giấu sâu trong giấc mơ, và chìa khóa khám phá nằm trong tay bạn. Xin đừng quên, chỉ trong giấc mơ mới tìm thấy câu trả lời.</t>
+          <t>Một cánh cổng quen thuộc xuất hiện trên vùng đất Rinascita, nối liền với thế giới mang tên Somnoire. Những ký ức xa xưa chôn sâu trong giấc mơ, và chìa khóa khám phá giờ nằm trong tay ngươi. Đừng quên, chỉ trong giấc mơ, câu trả lời mới được hé lộ.</t>
         </is>
       </c>
     </row>
@@ -1039,7 +1039,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Một cánh cổng quen thuộc xuất hiện trên vùng đất Rinascita, kết nối với một thế giới gọi là Somnoire. Những ký ức xưa chôn giấu sâu trong giấc mơ, và chìa khóa khám phá nằm trong tay bạn. Xin đừng quên, chỉ trong giấc mơ mới tìm thấy câu trả lời.</t>
+          <t>Một cánh cổng quen thuộc xuất hiện trên vùng đất Rinascita, nối liền với thế giới mang tên Somnoire. Những ký ức xa xưa chôn sâu trong giấc mơ, và chìa khóa khám phá giờ nằm trong tay ngươi. Đừng quên, chỉ trong giấc mơ, câu trả lời mới được hé lộ.</t>
         </is>
       </c>
     </row>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Một cánh cổng quen thuộc xuất hiện trên vùng đất Rinascita, kết nối với một thế giới gọi là Somnoire. Những ký ức xưa chôn giấu sâu trong giấc mơ, và chìa khóa khám phá nằm trong tay bạn. Xin đừng quên, chỉ trong giấc mơ mới tìm thấy câu trả lời.</t>
+          <t>Một cánh cổng quen thuộc xuất hiện trên vùng đất Rinascita, nối liền với thế giới mang tên Somnoire. Những ký ức xa xưa chôn sâu trong giấc mơ, và chìa khóa khám phá giờ nằm trong tay ngươi. Đừng quên, chỉ trong giấc mơ, câu trả lời mới được hé lộ.</t>
         </is>
       </c>
     </row>
@@ -1169,7 +1169,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Một cánh cổng quen thuộc xuất hiện trên vùng đất Rinascita, kết nối với một thế giới gọi là Somnoire. Những ký ức xưa chôn giấu sâu trong giấc mơ, và chìa khóa khám phá nằm trong tay bạn. Xin đừng quên, chỉ trong giấc mơ mới tìm thấy câu trả lời.</t>
+          <t>Một cánh cổng quen thuộc xuất hiện trên vùng đất Rinascita, nối liền với thế giới mang tên Somnoire. Những ký ức xa xưa chôn sâu trong giấc mơ, và chìa khóa khám phá giờ nằm trong tay ngươi. Đừng quên, chỉ trong giấc mơ, câu trả lời mới được hé lộ.</t>
         </is>
       </c>
     </row>
@@ -1234,7 +1234,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Một cánh cổng quen thuộc xuất hiện trên vùng đất Rinascita, kết nối với một thế giới gọi là Somnoire. Những ký ức xưa chôn giấu sâu trong giấc mơ, và chìa khóa khám phá nằm trong tay bạn. Xin đừng quên, chỉ trong giấc mơ mới tìm thấy câu trả lời.</t>
+          <t>Một cánh cổng quen thuộc xuất hiện trên vùng đất Rinascita, nối liền với thế giới mang tên Somnoire. Những ký ức xa xưa chôn sâu trong giấc mơ, và chìa khóa khám phá giờ nằm trong tay ngươi. Đừng quên, chỉ trong giấc mơ, câu trả lời mới được hé lộ.</t>
         </is>
       </c>
     </row>
@@ -1301,7 +1301,7 @@
       <c r="M13" t="inlineStr">
         <is>
           <t>"Không, hắn đã hứa với cái chết mà không giữ lời."
-Giúp Dorothy đánh bại quái vật sau cánh cửa.</t>
+Hãy giúp Dorothy đánh bại con quái vật sau cánh cửa.</t>
         </is>
       </c>
     </row>
@@ -1367,8 +1367,8 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>"Khi bạn nghĩ mọi chuyện đã kết thúc, thực ra mới chỉ là bắt đầu."
-Hãy thử thách kẻ địch đặc biệt phía sau cánh cửa. Good luck.</t>
+          <t>"Vừa nghĩ là mọi chuyện kết thúc, thì hóa ra mới chỉ bắt đầu thôi."
+Hãy thử thách kẻ địch đặc biệt phía sau cánh cửa đi. Chúc may mắn.</t>
         </is>
       </c>
     </row>
@@ -1434,8 +1434,8 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>"Cậu ước điều gì, và điều đó sẽ thuộc về cậu... Đến cuối cùng, mọi thứ thuộc về cậu rồi cũng sẽ quay về với cậu."
-Giúp Dorothy đánh bại quái vật sau cánh cửa.</t>
+          <t>"Cậu ước điều gì, và nó sẽ thuộc về cậu... Nhưng cuối cùng, tất cả những gì thuộc về cậu rồi cũng sẽ quay về với cậu."
+Hãy giúp Dorothy đánh bại con quái vật sau cánh cửa.</t>
         </is>
       </c>
     </row>
@@ -1501,8 +1501,8 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>"Cậu nghĩ mình đang gào thét, nhưng thực ra đó là..."
-Hãy thử thách kẻ địch đặc biệt phía sau cánh cửa. Good luck.</t>
+          <t>"Mày tưởng mình đang gào thét à, nhưng thực ra..."
+Hãy thử thách kẻ địch đặc biệt sau cánh cửa kia đi. Chúc may mắn.</t>
         </is>
       </c>
     </row>
@@ -1568,8 +1568,8 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>"Chúng trôi nổi... và cậu cũng sẽ trôi nổi thôi."
-Giúp Dorothy đánh bại quái vật sau cánh cửa.</t>
+          <t>"Chúng lơ lửng... và ngươi cũng sẽ lơ lửng theo thôi."
+Hãy giúp Dorothy đánh bại quái vật sau cánh cửa.</t>
         </is>
       </c>
     </row>
@@ -1635,8 +1635,8 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>"Con người có thể quên đi những điều quan trọng, nhưng chúng sẽ quay lại trong giấc mơ."
-Hãy thử thách kẻ địch đặc biệt phía sau cánh cửa. Good luck.</t>
+          <t>"Con người có thể quên đi những điều quan trọng, nhưng chúng sẽ lại bò về trong giấc mơ ta.
+Hãy thử thách kẻ địch đặc biệt sau cánh cửa. Chúc may mắn."</t>
         </is>
       </c>
     </row>
@@ -1702,8 +1702,8 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>"Một, hai, nó đang đến tìm cậu..."
-Giúp Dorothy đánh bại quái vật sau cánh cửa.</t>
+          <t>"Một, hai, nó đang đến với cậu đấy..."
+Giúp Dorothy đánh bại con quái vật sau cánh cửa đi.</t>
         </is>
       </c>
     </row>
@@ -1769,8 +1769,8 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>"Ba, bốn, khóa cửa chặt nào..."
-Hãy thử thách kẻ địch đặc biệt sau cánh cửa. Good luck.</t>
+          <t>"Một, hai, ba, bốn, khóa cửa lại nào..."
+Thử thách kẻ địch đặc biệt sau cánh cửa đi. Chúc may mắn nhé.</t>
         </is>
       </c>
     </row>
@@ -1836,8 +1836,8 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>"Dù trong vực thẳm sâu nhất, vẫn có thể sinh ra điều đẹp đẽ."
-Giúp Dorothy đánh bại quái vật sau cánh cửa.</t>
+          <t>"Ngay cả trong vực thẳm sâu nhất, vẫn có thể nảy sinh điều đẹp đẽ."
+Hãy giúp Dorothy đánh bại con quái vật sau cánh cửa.</t>
         </is>
       </c>
     </row>
@@ -1903,8 +1903,8 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>"Nghi lễ có thể thất bại, nhưng nó có thể xua đuổi thứ tồi tệ hơn—nỗi sợ hãi."
-Hãy thử thách kẻ địch đặc biệt phía sau cánh cửa. Good luck.</t>
+          <t>"Nghi lễ có thể thất bại, nhưng ít nhất nó có thể xua đi điều tồi tệ hơn—nỗi sợ hãi."
+Hãy thử thách kẻ địch đặc biệt phía sau cánh cửa. Chúc may mắn.</t>
         </is>
       </c>
     </row>
@@ -1970,8 +1970,8 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Những tần số kỳ lạ sôi sục trong Somnoire, dần dần thành hình thành một thứ gì đó quen thuộc.
-Nó phải trở về Vực Mộng Mị.</t>
+          <t>Những tần số kỳ dị sôi sục trong Somnoire, dần dần hiện hình thành thứ gì đó quen thuộc.
+Nó phải trở về Vực Mộng Mơ.</t>
         </is>
       </c>
     </row>
@@ -2037,8 +2037,8 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Yesterday vẫn sống mãi qua ngày mai. Những gì ngươi đã làm sẽ định hình thế giới sắp tới.
-Nó phải trở về Vực Mộng.</t>
+          <t>Hôm qua vẫn sống mãi vượt qua ngày mai. Những gì ngươi đã làm sẽ định hình thế giới chưa tới.
+Nó phải trở về Vực Mộng Mơ.</t>
         </is>
       </c>
     </row>
@@ -2104,8 +2104,8 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Cooldown sinh: 10 giây (Chơi đơn &amp; Hợp tác)
-&lt;color=#aa9b6a&gt;Resonators thử nghiệm sẽ khả dụng trong chế độ Chơi đơn.&lt;/color&gt;</t>
+          <t>Thời gian hồi sinh: 10 giây (Solo &amp; Co-op)
+&lt;color=#aa9b6a&gt;Resonator thử nghiệm sẽ xuất hiện trong chế độ Solo.&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -2172,9 +2172,9 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Cooldown sinh: 15s (Solo); 10s (Co-op)
-&lt;color=#aa9b6a&gt;Resonators thử nghiệm sẽ khả dụng trong chế độ Solo.&lt;/color&gt;
-Khi HP của kẻ địch dưới 50%, nhận khiên tương đương 30% HP tối đa. Khi được khiên bảo vệ, ATK của kẻ địch tăng 50%, nhưng DMG từ Resonance Liberation chúng nhận sẽ tăng 100%.</t>
+          <t>Thời gian hồi sinh: 15 giây (Solo); 10 giây (Co-op)
+&lt;color=#aa9b6a&gt;Resonator thử nghiệm sẽ xuất hiện trong chế độ Solo.&lt;/color&gt;
+Khi HP dưới 50%, kẻ địch nhận khiên tương đương 30% HP tối đa. Khi có khiên, ATK của kẻ địch tăng 50%, nhưng DMG Resonance Liberation nhận vào tăng 100%.</t>
         </is>
       </c>
     </row>
@@ -2240,8 +2240,8 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Cooldown sinh: 10 giây (Chơi đơn &amp; Hợp tác)
-&lt;color=#aa9b6a&gt;Resonators thử nghiệm sẽ khả dụng trong chế độ Chơi đơn.&lt;/color&gt;</t>
+          <t>Thời gian hồi sinh: 10 giây (Solo &amp; Co-op)
+&lt;color=#aa9b6a&gt;Resonator thử nghiệm sẽ xuất hiện trong chế độ Solo.&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -2308,9 +2308,9 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Cooldown sinh: 15 giây (Solo); 10 giây (Co-op)
-&lt;color=#aa9b6a&gt;Resonators thử nghiệm sẽ xuất hiện trong chế độ Solo.&lt;/color&gt;
-DMG nhận vào của kẻ địch giảm 30%. Khi bị Hóa Đá, DMG nhận vào tăng 100%.</t>
+          <t>Thời gian hồi sinh: 15 giây (Solo); 10 giây (Co-op)
+&lt;color=#aa9b6a&gt;Resonator thử nghiệm sẽ xuất hiện trong chế độ Solo.&lt;/color&gt;
+Kẻ địch giảm 30% DMG nhận vào. Khi bị bất động, DMG nhận vào tăng 100%.</t>
         </is>
       </c>
     </row>
@@ -2376,8 +2376,8 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Cooldown sinh: 10 giây (Chơi đơn &amp; Hợp tác)
-&lt;color=#aa9b6a&gt;Resonators thử nghiệm sẽ khả dụng trong chế độ Chơi đơn.&lt;/color&gt;</t>
+          <t>Thời gian hồi sinh: 10 giây (Solo &amp; Co-op)
+&lt;color=#aa9b6a&gt;Resonator thử nghiệm sẽ xuất hiện trong chế độ Solo.&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -2444,9 +2444,9 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Cooldown sinh: 15s (Solo); 10s (Co-op)
-&lt;color=#aa9b6a&gt;Resonators thử nghiệm sẽ xuất hiện trong chế độ Solo.&lt;/color&gt;
-DMG nhận vào của Resonators không đủ HP sẽ tăng 50%, trong khi DMG nhận vào của Resonators đủ HP sẽ giảm 50%.</t>
+          <t>Thời gian hồi sinh: 15 giây (Solo); 10 giây (Co-op)
+&lt;color=#aa9b6a&gt;Resonator thử nghiệm sẽ xuất hiện trong chế độ Solo.&lt;/color&gt;
+Resonator không đủ HP nhận DMG tăng 50%, Resonator đủ HP nhận DMG giảm 50%.</t>
         </is>
       </c>
     </row>
@@ -2512,8 +2512,8 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Cooldown sinh: 10 giây (Chơi đơn &amp; Hợp tác)
-&lt;color=#aa9b6a&gt;Resonators thử nghiệm sẽ khả dụng trong chế độ Chơi đơn.&lt;/color&gt;</t>
+          <t>Thời gian hồi sinh: 10 giây (Solo &amp; Co-op)
+&lt;color=#aa9b6a&gt;Resonator thử nghiệm sẽ xuất hiện trong chế độ Solo.&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -2580,9 +2580,9 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Cooldown Sinh: 15 giây (Chơi đơn); 10 giây (Chơi cùng)
-&lt;color=#aa9b6a&gt;Resonators thử nghiệm sẽ xuất hiện trong chế độ Chơi đơn.&lt;/color&gt;
-DMG gây ra bởi kẻ địch trên không tăng 50%. Khi bị tấn công trên không, kẻ địch nhận 1 tầng Panic, kích hoạt mỗi giây.</t>
+          <t>Thời gian hồi sinh: 15 giây (Solo); 10 giây (Co-op)
+&lt;color=#aa9b6a&gt;Resonator thử nghiệm sẽ xuất hiện trong chế độ Solo.&lt;/color&gt;
+DMG gây ra khi kẻ địch ở trên không tăng 50%. Mỗi lần bị đánh trên không, kẻ địch nhận 1 tầng Hoảng Loạn, kích hoạt mỗi giây 1 lần.</t>
         </is>
       </c>
     </row>
@@ -2648,8 +2648,8 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Cooldown sinh: 10 giây (Chơi đơn &amp; Hợp tác)
-&lt;color=#aa9b6a&gt;Resonators thử nghiệm sẽ khả dụng trong chế độ Chơi đơn.&lt;/color&gt;</t>
+          <t>Thời gian hồi sinh: 10 giây (Solo &amp; Co-op)
+&lt;color=#aa9b6a&gt;Resonator thử nghiệm sẽ xuất hiện trong chế độ Solo.&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -2716,9 +2716,9 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>Cooldown sinh: 15 giây (Solo); 10 giây (Co-op)
-&lt;color=#aa9b6a&gt;Resonators thử nghiệm sẽ khả dụng trong chế độ Solo.&lt;/color&gt;
-Khi kẻ địch gây DMG, chúng nhận 1 tầng Sợ Hãi Mê Loạn. Mỗi tầng tăng 5% DMG gây ra và giảm 5% DMG nhận vào, cộng dồn tối đa 10 tầng, kích hoạt mỗi giây. Nhận DMG từ Resonance Skill sẽ xóa 1 tầng Sợ Hãi Mê Loạn của kẻ địch, kích hoạt mỗi giây. DMG từ Resonance Skill mà kẻ địch nhận tăng 100%.</t>
+          <t>Thời gian hồi sinh: 15 giây (Solo); 10 giây (Co-op)
+&lt;color=#aa9b6a&gt;Resonator thử nghiệm sẽ xuất hiện trong chế độ Solo.&lt;/color&gt;
+Mỗi khi gây DMG, kẻ địch nhận 1 tầng Sợ Hãi Mê Loạn. Mỗi tầng tăng 5% DMG gây ra và giảm 5% DMG nhận vào, tối đa 10 tầng, kích hoạt mỗi giây 1 lần. Khi nhận DMG Resonance Skill, kẻ địch mất 1 tầng Sợ Hãi Mê Loạn, kích hoạt mỗi giây 1 lần. DMG Resonance Skill nhận vào tăng 100%.</t>
         </is>
       </c>
     </row>
@@ -2784,8 +2784,8 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>Cooldown sinh: 10 giây (Chơi đơn &amp; Hợp tác)
-&lt;color=#aa9b6a&gt;Resonators thử nghiệm sẽ khả dụng trong chế độ Chơi đơn.&lt;/color&gt;</t>
+          <t>Thời gian hồi sinh: 10 giây (Solo &amp; Co-op)
+&lt;color=#aa9b6a&gt;Resonator thử nghiệm sẽ xuất hiện trong chế độ Solo.&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -2852,9 +2852,9 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>Cooldown sinh: 15 giây (Solo); 10 giây (Co-op)
-&lt;color=#aa9b6a&gt;Resonators thử nghiệm sẽ xuất hiện ở chế độ Solo.&lt;/color&gt;
-ATK của kẻ địch tăng 10% mỗi 10 giây, không giới hạn. Khi bị Hóa Đá, mất toàn bộ buff. ATK của tất cả Resonators trong đội tăng 10% mỗi 10 giây, không giới hạn. Resonators có HP dưới 50% sẽ mất toàn bộ buff.</t>
+          <t>Thời gian hồi sinh: 15 giây (Solo); 10 giây (Co-op)
+&lt;color=#aa9b6a&gt;Resonator thử nghiệm sẽ xuất hiện trong chế độ Solo.&lt;/color&gt;
+Mỗi 10 giây, ATK của kẻ địch tăng 10%, không giới hạn. Khi bị bất động, tất cả buff sẽ bị loại bỏ. Mỗi 10 giây, ATK của tất cả Resonator trong đội tăng 10%, không giới hạn. Resonator dưới 50% HP sẽ mất hết buff.</t>
         </is>
       </c>
     </row>
@@ -2919,7 +2919,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>Thử thách Hàng tuần: Light Bình Minh</t>
+          <t>Thử Thách Hàng Tuần: Ánh Sáng Bình Minh</t>
         </is>
       </c>
     </row>
@@ -2985,8 +2985,8 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Từ thế giới đảo ngược, bạn thoáng thấy chân lý của lời tiên tri.
-Vòng xoay định mệnh bắt đầu chuyển động, khi bạn xé toạc lời dối trá vô tận treo lơ lửng trên bầu trời, lao về phía "trận chiến cuối cùng" của mình.</t>
+          <t>Từ thế giới đảo ngược, ngươi thoáng thấy chân tướng của lời tiên tri.
+Bánh xe định mệnh bắt đầu quay, khi ngươi xé toạc lớp dối trá vô tận treo lơ lửng trên bầu trời, lao về phía "trận chiến cuối cùng" của mình.</t>
         </is>
       </c>
     </row>
@@ -3051,7 +3051,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>Một nhà ngục treo lơ lửng trên trời, nuốt chửng vinh quang của quá khứ. Trên ngai vàng thần thánh phủ đầy gai nhọn, nàng chờ đợi sự diệt vong của mình.</t>
+          <t>Một nhà tù treo lơ lửng trên bầu trời, nuốt chửng vinh quang của quá khứ. Trên ngai vàng thần thánh phủ đầy gai nhọn, nàng chờ đợi cái chết của chính mình.</t>
         </is>
       </c>
     </row>
@@ -3117,8 +3117,8 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>Nơi đây, quá khứ và tương lai đan xen. Những giọt nước mắt và máu đổ trong Divine Trials lan tỏa và biến dạng thành Sea of Ghosts như ngày nay.
-Trên những con sóng ấy là những tiếng nức nở lặng thầm, những tiếng thở dài cay đắng, và quá khứ không lời của gia tộc Fisalia...</t>
+          <t>Nơi đây, quá khứ và tương lai đan xen. Máu và nước mắt đổ xuống trong Thánh Thử Thách lan tỏa, xoắn vặn thành biển cả ngày nay – Biển Ma.
+Trên những con sóng ấy là tiếng nức nở lặng thầm, tiếng thở dài cay đắng, và quá khứ không lời của gia tộc Fisalia...</t>
         </is>
       </c>
     </row>
@@ -3250,7 +3250,7 @@
       <c r="M42" t="inlineStr">
         <is>
           <t>Quá khứ trì trệ, lên men theo thời gian thành những tần số dị thường, giờ đây nhấn chìm cả tòa lâu đài.
-Liệu có ai đáp lại tiếng gọi của những linh hồn? Dù giọng nói của họ chỉ còn mong manh như tiếng bong bóng vỡ tan?</t>
+Liệu có ai đáp lại tiếng gọi của những oan hồn? Dù giọng nói của họ chỉ còn mong manh như tiếng bong bóng vỡ tan?</t>
         </is>
       </c>
     </row>
@@ -3315,7 +3315,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>Ngõ Tối</t>
+          <t>Black Alley</t>
         </is>
       </c>
     </row>
@@ -3380,7 +3380,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>Những đường thủy cổ xưa dưới lòng đất này đã trở thành sào huyệt của bọn tội phạm. Hãy cùng Zani mạo hiểm vào trong để triệt phá tội ác lan tràn ở đây.</t>
+          <t>Những dòng kênh ngầm cổ xưa này đã trở thành sào huyệt của bọn tội phạm. Hãy cùng Zani xâm nhập vào trong để triệt phá tội ác đang lan tràn ở đây.</t>
         </is>
       </c>
     </row>
@@ -3445,7 +3445,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>Những đường thủy cổ xưa dưới lòng đất này đã trở thành sào huyệt của bọn tội phạm. Hãy cùng Zani mạo hiểm vào trong để triệt phá tội ác lan tràn ở đây.</t>
+          <t>Những dòng kênh ngầm cổ xưa này đã trở thành sào huyệt của bọn tội phạm. Hãy cùng Zani xâm nhập vào trong để triệt phá tội ác đang lan tràn ở đây.</t>
         </is>
       </c>
     </row>
@@ -3575,7 +3575,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>Mô tả màn demo Ma Cà Rồng 01</t>
+          <t>Màn thử nghiệm ma cà rồng - Cấp độ 01</t>
         </is>
       </c>
     </row>
@@ -3640,7 +3640,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>Mô tả màn demo Ma Cà Rồng 02</t>
+          <t>Mô tả màn thử nghiệm ma cà rồng - Cấp độ 02</t>
         </is>
       </c>
     </row>
@@ -3705,7 +3705,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>Mô tả màn demo Ma Cà Rồng 03</t>
+          <t>Mô tả màn thử nghiệm ma cà rồng - Cấp độ 03</t>
         </is>
       </c>
     </row>
@@ -3770,7 +3770,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>Mô tả màn demo Ma Cà Rồng 04</t>
+          <t>Mô tả màn thử nghiệm ma cà rồng - Cấp độ 04</t>
         </is>
       </c>
     </row>
@@ -3835,7 +3835,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>Mô tả màn demo Ma Cà Rồng 05</t>
+          <t>Mô tả màn thử nghiệm ma cà rồng - Cấp độ 05</t>
         </is>
       </c>
     </row>
@@ -3900,7 +3900,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>Mô tả màn demo Ma Cà Rồng 06</t>
+          <t>Mô tả màn thử nghiệm ma cà rồng - Cấp độ 06</t>
         </is>
       </c>
     </row>
@@ -3965,7 +3965,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>Mô tả màn demo Ma Cà Rồng 07</t>
+          <t>Mô tả màn chơi thử nghiệm ma cà rồng - Cấp 07</t>
         </is>
       </c>
     </row>
@@ -4030,7 +4030,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>The Beyond—nơi từng hứa hẹn sự hoàn hảo—giờ không còn tồn tại trên thế giới này, ít nhất là hiện tại. Nhưng sâu dưới đáy biển, những mảnh vỡ của nó vẫn lấp lánh với những tiếng vọng của nỗi ám ảnh và hy vọng xưa cũ. Mỗi lần anh trở lại, anh sẽ nghe thấy tiếng cười vui vẻ của sự tái sinh, như thể vùng đất này vẫn còn giữ lời hứa về sự vĩnh cửu.</t>
+          <t>Thế Giới Bên Kia—nơi từng hứa hẹn sự hoàn hảo—giờ không còn tồn tại trên thế giới này, ít nhất là hiện tại. Nhưng sâu dưới lòng biển, những mảnh vỡ tan tành của nó vẫn lấp lánh, vang vọng những ám ảnh và hy vọng xưa cũ. Mỗi lần cậu trở về, sẽ nghe thấy tiếng cười vui mừng của sự tái sinh, như thể vùng đất này vẫn còn giữ lời hứa về sự vĩnh cửu.</t>
         </is>
       </c>
     </row>
@@ -4095,7 +4095,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>Thử Thách Hàng Tuần: Cơn Đại Họa Cindernite</t>
+          <t>Thử Thách Hàng Tuần: Đại Họa Cindernite</t>
         </is>
       </c>
     </row>
@@ -4161,8 +4161,8 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>Cơn thịnh nộ của Thần Tính lại một lần nữa giáng xuống, lan truyền lời tiên tri diệt vong như thủy triều tràn.
-Một lần nữa, hy vọng vượt qua nỗi sợ hãi và bóng tối để thắp sáng đêm dài vĩnh cửu.</t>
+          <t>Cơn thịnh nộ của Thần Tính lại giáng xuống, truyền bá lời tiên tri diệt vong như thủy triều tràn bờ.
+Một lần nữa, hy vọng vượt lên nỗi sợ hãi và bóng tối để soi sáng đêm dài vĩnh cửu.</t>
         </is>
       </c>
     </row>
@@ -4227,7 +4227,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>Leviathan Threnodian đã hợp nhất ký ức, cảm xúc và khát vọng của tất cả Rinascitan thành một Vương quốc, đồng hóa suy nghĩ và xóa bỏ những ám ảnh của họ. Một Thiên đường hoàn hảo được vẽ nên từ những linh hồn hoang mang, những thân thể vô hồn hát đồng thanh ngày đêm—chỉ để kiếm được ân sủng và sự cứu rỗi của Ngài.</t>
+          <t>Threnodian Leviathan đã hợp nhất ký ức, cảm xúc và khát vọng của tất cả người Rinascita, đồng hóa suy nghĩ và xóa bỏ những ám ảnh của họ. Một Thiên Đường hoàn hảo được vẽ nên trên những linh hồn hoang mang, những thân xác vô hồn ngày đêm tụng niệm—chỉ để mong được ân sủng và cứu rỗi từ Ngài.</t>
         </is>
       </c>
     </row>
@@ -4358,8 +4358,8 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>Không gian dữ liệu bên trong Di Vật Sentinel, Civilization Capsule.
-Những gì bị lãng quên bắt đầu trỗi dậy. Những gì bị phong ấn đang dần hé lộ...</t>
+          <t>Không gian dữ liệu bên trong Di Vật Cảnh Vệ, Viên Nang Văn Minh.
+Những gì bị lãng quên bắt đầu trỗi dậy. Những gì bị phong ấn đang tiến gần đến sự thật...</t>
         </is>
       </c>
     </row>
@@ -4424,7 +4424,7 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>Mặt Phẳng Thủy Triều Tối</t>
+          <t>Tầng Thủy Triều Hắc Ám</t>
         </is>
       </c>
     </row>
@@ -4490,8 +4490,8 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>Một thế giới khác ẩn mình trong Thủy Triều Hắc Ám. Từ sâu thẳm vọng ra những lời thì thầm của "Thần Tính" cổ xưa, nguồn cội của mọi độc ác và sợ hãi.
-Thế giới ấy đang chờ đợi những ai dám bước vào.</t>
+          <t>Một thế giới khác ẩn mình trong Bóng Tối Thủy Triều. Từ vực sâu vọng lên những lời thì thầm của "Thần Tính" cổ xưa, nguồn cơn của mọi độc ác và sợ hãi.
+Thế giới ấy đang chờ đợi tất cả những ai dám bước vào.</t>
         </is>
       </c>
     </row>
@@ -4556,7 +4556,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>Một lối vào bí ẩn xuất hiện giữa Hắc Triều, nơi các dòng chảy cuộn xoáy hội tụ.</t>
+          <t>Một lối vào bí ẩn mở ra giữa Dòng Chảy Hắc Ám, nơi những dòng nước cuộn trào hội tụ.</t>
         </is>
       </c>
     </row>
@@ -4621,7 +4621,7 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>3.3 Academy Dungeon</t>
+          <t>3.3 Hầm Ngục Học Viện</t>
         </is>
       </c>
     </row>
@@ -4686,7 +4686,7 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>3.3 Academy Dungeon</t>
+          <t>3.3 Hầm Ngục Học Viện</t>
         </is>
       </c>
     </row>
@@ -4751,7 +4751,7 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>Hầm Ngục Honami City 3.3</t>
+          <t>3.3 Hầm Ngục Thành Phố Honami</t>
         </is>
       </c>
     </row>
@@ -4816,7 +4816,7 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>Hầm Ngục Honami City 3.3</t>
+          <t>3.3 Hầm Ngục Thành Phố Honami</t>
         </is>
       </c>
     </row>
@@ -4881,7 +4881,7 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>3.3 Viện Nghiên Cứu Dungeon</t>
+          <t>3.3 Hầm Ngục Viện Nghiên Cứu</t>
         </is>
       </c>
     </row>
@@ -4946,7 +4946,7 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>3.3 Viện Nghiên Cứu Dungeon</t>
+          <t>3.3 Hầm Ngục Viện Nghiên Cứu</t>
         </is>
       </c>
     </row>
@@ -5011,7 +5011,7 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>Kết Thúc Câu Chuyện 3.3 - Honami City</t>
+          <t>3.3 Kết Thúc Câu Chuyện Thành Phố Honami</t>
         </is>
       </c>
     </row>
@@ -5076,7 +5076,7 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>Kết Thúc Câu Chuyện 3.3 - Honami City</t>
+          <t>3.3 Kết Thúc Câu Chuyện Thành Phố Honami</t>
         </is>
       </c>
     </row>
@@ -5141,7 +5141,7 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>Spacetrek Collective Viện Nghiên Cứu là một cơ sở nghiên cứu không biên giới, nơi các nhà khoa học từ khắp nơi trên thế giới nghiên cứu về Exostrider và Stridergate. Đây cũng là trung tâm R&amp;D của mặt trời nhân tạo Helios. Được xây dựng tại điểm cao nhất ở Lahai-Roi, Viện nằm trên một đường ray quỹ đạo dọc theo Starward Riseway, liên tục giám sát thanh kiếm vĩ đại của Exostrider. Qua nhiều năm, vô số nhà nghiên cứu đã cống hiến cuộc đời và trí tuệ tại đây, tất cả đều với hy vọng ngọn đuốc khám phá của nhân loại sẽ mãi rực sáng.</t>
+          <t>Viện Nghiên Cứu Spacetrek Collective là một cơ sở nghiên cứu không biên giới, nơi các nhà khoa học từ khắp nơi trên thế giới nghiên cứu Exostrider và Stridergate. Đây cũng là trung tâm R&amp;D của mặt trời nhân tạo Helios. Đứng tại điểm cao nhất ở Lahai-Roi, Viện được xây dựng trên một đường ray quỹ đạo dọc theo Starward Riseway, liên tục theo dõi thanh kiếm vĩ đại của Exostrider. Qua bao năm tháng, vô số nhà nghiên cứu đã cống hiến cuộc đời và trí tuệ tại đây, tất cả đều với hy vọng ngọn đuốc khám phá của nhân loại sẽ mãi rực sáng.</t>
         </is>
       </c>
     </row>
@@ -5206,7 +5206,7 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>Startorch Academy cung cấp cho mỗi học viên một phòng ký túc riêng để thư giãn và nạp năng lượng. Mọi không gian trong tòa nhà đều được thiết kế tỉ mỉ nhằm đáp ứng đa dạng nhu cầu. Khu vực nghỉ ngơi tạo ra môi trường yên tĩnh giúp ngay cả những người mất ngủ cũng dễ dàng chìm vào giấc ngủ. Tường cách âm giảm thiểu tiếng ồn, đảm bảo sự yên bình.</t>
+          <t>Học viện Startorch cung cấp cho mỗi học viên một phòng ký túc xá riêng để nghỉ ngơi và nạp năng lượng. Mọi không gian trong tòa nhà đều được thiết kế tỉ mỉ để đáp ứng đa dạng nhu cầu. Khu vực nghỉ ngơi tạo ra môi trường thư giãn, giúp cả những người mất ngủ cũng dễ dàng chìm vào giấc ngủ. Tường cách âm giảm thiểu tiếng ồn, đảm bảo sự yên tĩnh tuyệt đối.</t>
         </is>
       </c>
     </row>
@@ -5272,8 +5272,8 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>Vùng đất linh thiêng của Roya và nơi ở của Lục Heliodic. Nơi này bảo vệ các bộ phận Exostrider và đóng vai trò là kho lưu trữ trung tâm cho tất cả hồ sơ của Roya.
-Với mỗi chu kỳ hoạt động của Reactor Drive, Solisylum sẽ tính toán độ ổn định, theo dõi sự ra đời và phát triển của Exoswarm, đồng thời giám sát sự trở lại của chúng với Exostrider.</t>
+          <t>Đất thiêng của Roya và nơi ngự trị của Lục Heliodic. Nơi đây bảo vệ các bộ phận Exostrider và lưu trữ kho lưu trữ trung tâm của tất cả hồ sơ Royan.
+Với mỗi chu kỳ hoạt động của Reactor Drive, Solisylum sẽ tính toán độ ổn định, theo dõi sự ra đời và phát triển của Exoswarm, cũng như giám sát sự trở về của chúng với Exostrider.</t>
         </is>
       </c>
     </row>
@@ -5338,7 +5338,7 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>Mở khóa sau khi hoàn thành điều kiện tiên quyết</t>
+          <t>Mở khóa sau khi hoàn thành điều kiện chơi trước</t>
         </is>
       </c>
     </row>
@@ -5403,7 +5403,7 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>Đạt Cấp Liên Minh 8 và xây dựng lại Farer's Road trong sự kiện “Operation: Frontier Renewal”</t>
+          <t>Đạt Cấp Liên Minh 8 và tái thiết Con Đường Người Đi Xa trong Sự Kiện “Chiến Dịch: Biên Cương Phục Hưng”.</t>
         </is>
       </c>
     </row>
@@ -5469,8 +5469,8 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>Trong sâu thẳm ký ức của những vì sao, một cỗ máy đang chờ đợi khoảnh khắc trở lại.
-Hãy lắng nghe một lần nữa những tiếng thở dài của hy vọng, đau đớn, lo âu và đau buồn, rồi phá vỡ những xiềng xích vĩnh cửu.</t>
+          <t>Trong ký ức sâu thẳm của những vì sao, một cỗ máy đang chờ đợi trong im lặng khoảnh khắc trở lại.
+Hãy lắng nghe một lần nữa những tiếng thở dài của hy vọng, đau đớn, lo âu và bi ai, rồi chặt đứt những xiềng xích vĩnh cửu.</t>
         </is>
       </c>
     </row>
@@ -5536,8 +5536,8 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>Giận dữ và nước mắt. Đau khổ và niềm vui. Nỗi buồn và đau đớn. Tất cả đều được cô đọng, cùng với tiếng thở dài của cô, thành một tần số vàng duy nhất.
-Nó nhìn lên bầu trời, chìm đắm trong những ký ức đã phai mờ theo thời gian. Người lữ khách lạc lối vẫn đang tìm đường về nhà.</t>
+          <t>Thịnh nộ và nước mắt. Đau khổ và niềm vui. Sầu bi và thống khổ. Tất cả hòa quyện cùng tiếng thở dài của nàng, cô đọng thành một tần số vàng óng.
+Nó ngước nhìn bầu trời, lạc trong những ký ức mỏng manh theo năm tháng. Người lữ khách lạc lối vẫn đang kiếm tìm con đường trở về nhà.</t>
         </is>
       </c>
     </row>
@@ -5733,7 +5733,7 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>Một bóng hình từ quá khứ, sinh ra khi "sự thật" chạm vào hư vô, trôi dạt bất tận trong đại dương hư không vô tận này.
+          <t>Một bóng hình từ quá khứ, sinh ra khi "sự thật" chạm vào hư vô, trôi dạt bất tận trong đại dương vô tận này.
 Hãy đến bên cô ấy. Gọi tên cô ấy. Đừng để cô ấy cô đơn.</t>
         </is>
       </c>
@@ -5801,9 +5801,9 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>Một sinh vật chỉ tồn tại vì Aleph-1. Ngay cả nụ cười dịu dàng của cô ấy cũng đã bị tước đi.
-Cái tên, danh tính, Forte, thậm chí cả mối quan hệ với người khác… tất cả đều là dối trá.
-Thế nhưng, thế giới sẽ không chìm vào bóng tối vô tận. Điểm cuối con đường cô ấy đi không thể là hư vô vĩnh cửu.</t>
+          <t>Một sinh vật chỉ tồn tại vì Aleph-1. Ngay cả nụ cười dịu dàng của cô cũng đã bị cướp mất.
+Tên tuổi, danh tính, Forte, thậm chí cả mối quan hệ với người khác… tất cả đều là dối trá.
+Thế nhưng, thế giới sẽ không chìm trong bóng tối vô tận. Con đường cô đi không thể kết thúc bằng hư vô vĩnh cửu.</t>
         </is>
       </c>
     </row>
@@ -6258,7 +6258,7 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>Xin lỗi, {PlayerName}. Cho tôi xin chút thời gian của anh được không?</t>
+          <t>Xin lỗi {PlayerName}. Cho tớ xin chút thời gian của cậu được không?</t>
         </is>
       </c>
     </row>
@@ -6323,7 +6323,7 @@
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>Chúng tôi đang tiến hành giai đoạn thử nghiệm mới cho dự án nghiên cứu mà bạn đã tham gia trước đây. Bạn có muốn tham gia lại không?</t>
+          <t>Chúng tôi đang tiến hành giai đoạn thử nghiệm mới cho dự án nghiên cứu mà trước đây cậu đã tham gia. Cậu có muốn tham gia lại không?</t>
         </is>
       </c>
     </row>
@@ -6388,7 +6388,7 @@
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>Tôi quan tâm.</t>
+          <t>Tớ quan tâm đấy.</t>
         </is>
       </c>
     </row>
@@ -6453,7 +6453,7 @@
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>Tôi không quan tâm.</t>
+          <t>Tôi không hứng thú.</t>
         </is>
       </c>
     </row>
@@ -6518,7 +6518,7 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>Great. Để tôi giới thiệu lại nghiên cứu của chúng ta.</t>
+          <t>Tuyệt. Để tôi giới thiệu lại nghiên cứu của chúng ta một lần nữa.</t>
         </is>
       </c>
     </row>
@@ -6583,7 +6583,7 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>Bạn chưa cần từ chối vội. Hãy để tôi giới thiệu lại nghiên cứu của chúng tôi một lần nữa.</t>
+          <t>Không cần từ chối vội. Để tớ giới thiệu lại nghiên cứu của chúng ta một lần nữa.</t>
         </is>
       </c>
     </row>
@@ -6648,7 +6648,7 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>Chắc hẳn cậu đã từng trải qua khu huấn luyện mô phỏng của Huấn luyện viên Yhan rồi nhỉ.</t>
+          <t>Tôi tin là cậu đã từng trải qua khu huấn luyện mô phỏng của Hướng dẫn viên Yhan rồi.</t>
         </is>
       </c>
     </row>
@@ -6713,7 +6713,7 @@
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>Nơi các chiến binh của chúng ta luyện tập chống lại hình ảnh toàn ký của kẻ địch và cải thiện kỹ năng chiến đấu.</t>
+          <t>Nơi các chiến binh của ta rèn luyện trước những đối thủ ảo và nâng cao kỹ năng chiến đấu.</t>
         </is>
       </c>
     </row>
@@ -6778,7 +6778,7 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>Trước đây, Học Viện đã bắt đầu thử nghiệm công nghệ "hình chiếu" cải tiến để mô phỏng những kẻ địch mạnh hơn.</t>
+          <t>Trước đây, Học viện đã bắt đầu thử nghiệm công nghệ "hình chiếu" cải tiến để mô phỏng những kẻ địch mạnh hơn.</t>
         </is>
       </c>
     </row>
@@ -6843,7 +6843,7 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>Nếu công nghệ này được chứng minh hiệu quả, chúng ta có thể cung cấp đào tạo toàn diện hơn cho binh lính. Điều này đồng nghĩa với kết quả tốt hơn cho mọi nhu cầu của họ.</t>
+          <t>Nếu công nghệ này được chứng minh là hiệu quả, chúng ta có thể cung cấp huấn luyện toàn diện hơn cho binh lính. Điều đó đồng nghĩa với kết quả tốt hơn cho nhu cầu tổng thể của họ.</t>
         </is>
       </c>
     </row>
@@ -6908,7 +6908,7 @@
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>Chúng ta đã đạt được những đột phá kỹ thuật đáng kể từ lần thử nghiệm trước, nhưng nhiều chi tiết nhỏ vẫn cần được hoàn thiện.</t>
+          <t>Ta đã đạt được những đột phá kỹ thuật đáng kể từ lần thử nghiệm trước, nhưng vẫn còn nhiều chi tiết nhỏ cần phải hoàn thiện.</t>
         </is>
       </c>
     </row>
@@ -6973,7 +6973,7 @@
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>Bạn có sẵn lòng thử nghiệm cho chúng tôi và tiếp tục hỗ trợ nghiên cứu không?</t>
+          <t>Cậu có sẵn lòng thử nghiệm nó cho chúng tớ và tiếp tục hỗ trợ nghiên cứu không?</t>
         </is>
       </c>
     </row>
@@ -7038,7 +7038,7 @@
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>Để tôi lo.</t>
+          <t>Để đó cho ta.</t>
         </is>
       </c>
     </row>
@@ -7168,7 +7168,7 @@
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>Có ưu đãi cho khách hàng lâu năm không?</t>
+          <t>Có ưu đãi gì cho khách hàng lâu năm không?</t>
         </is>
       </c>
     </row>
@@ -7233,7 +7233,7 @@
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>Tớ biết là có thể tin tưởng cậu mà.</t>
+          <t>Tớ biết là có thể trông cậy vào cậu mà.</t>
         </is>
       </c>
     </row>
@@ -7298,7 +7298,7 @@
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>Lối vào mô phỏng nằm ngay bên cạnh tôi. Chúc bạn may mắn.</t>
+          <t>Lối vào mô phỏng nằm ngay bên cạnh ta. Chúc cậu may mắn.</t>
         </is>
       </c>
     </row>
@@ -7363,7 +7363,7 @@
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>Yên tâm, với tư cách là người tham gia xuất sắc nhất trong đợt thử nghiệm trước, những nỗ lực của bạn sẽ được hỗ trợ bởi những nguồn lực tốt nhất mà Học viện có thể cung cấp.</t>
+          <t>Yên tâm đi, với tư cách là người đứng đầu trong đợt thử nghiệm trước, nỗ lực của ngươi sẽ được hỗ trợ bởi những nguồn lực tốt nhất mà Học viện có thể cung cấp.</t>
         </is>
       </c>
     </row>
@@ -7428,7 +7428,7 @@
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>Lối vào mô phỏng nằm ngay bên cạnh tôi. Tin tôi đi, phần thưởng sẽ không làm bạn thất vọng đâu.</t>
+          <t>Lối vào mô phỏng nằm ngay bên cạnh ta. Tin ta đi, phần thưởng sẽ không làm cậu thất vọng đâu.</t>
         </is>
       </c>
     </row>
@@ -7493,7 +7493,7 @@
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>Dữ liệu từ thí nghiệm này cũng có vẻ khả quan...</t>
+          <t>Dữ liệu từ thí nghiệm này cũng cho kết quả khả quan...</t>
         </is>
       </c>
     </row>
@@ -7623,7 +7623,7 @@
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>Chào {PlayerName}. Bạn đã thử nghiệm công nghệ mới nhất của chúng tôi chưa?</t>
+          <t>Chào {PlayerName}. Cậu đã thử nghiệm công nghệ mới nhất của chúng tớ chưa?</t>
         </is>
       </c>
     </row>
@@ -7688,7 +7688,7 @@
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>Vâng, tôi có.</t>
+          <t>Ừ, ta có.</t>
         </is>
       </c>
     </row>
@@ -7753,7 +7753,7 @@
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>Chưa xong.</t>
+          <t>Chưa.</t>
         </is>
       </c>
     </row>
@@ -7818,7 +7818,7 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>Mọi người ở phòng thí nghiệm đã rất hào hứng khi biết bạn sẽ hỗ trợ nghiên cứu của chúng tôi lần nữa.</t>
+          <t>Mọi người ở phòng thí nghiệm đã rất háo hức khi nghe tin cậu sẽ hỗ trợ nghiên cứu của chúng tôi lần nữa.</t>
         </is>
       </c>
     </row>
@@ -7883,7 +7883,7 @@
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>Với sự trợ giúp của bạn, tôi tin rằng công nghệ của chúng ta sẽ sớm đạt đến tiềm năng tối đa để binh lính có thể sử dụng.</t>
+          <t>Nhờ sự hỗ trợ của cậu, ta tin rằng công nghệ của chúng ta sẽ sớm đạt đến tiềm năng tối đa để binh lính có thể sử dụng.</t>
         </is>
       </c>
     </row>
@@ -7948,7 +7948,7 @@
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>À, nhớ ghé xem khi nào rảnh nhé. Tôi đã đăng ký sẵn cho bạn rồi.</t>
+          <t>À, nhớ ghé xem khi nào rảnh nhé. Tôi đã đăng ký giúp cậu rồi.</t>
         </is>
       </c>
     </row>
@@ -8013,7 +8013,7 @@
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>Mọi người ở phòng thí nghiệm đã rất hào hứng khi biết bạn sẽ hỗ trợ nghiên cứu của chúng tôi lần nữa.</t>
+          <t>Mọi người ở phòng thí nghiệm đã rất háo hức khi nghe tin cậu sẽ hỗ trợ nghiên cứu của chúng tôi lần nữa.</t>
         </is>
       </c>
     </row>
@@ -8078,7 +8078,7 @@
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>Cánh cổng dẫn đến Somnoire lại mở… Có chuyện gì xảy ra sao?</t>
+          <t>Cổng vào Somnoire lại mở rồi… Có chuyện gì xảy ra sao?</t>
         </is>
       </c>
     </row>
@@ -8143,7 +8143,7 @@
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>À, cậu đây rồi! Cảm ơn vì đã giúp chúng tôi dọn dẹp mớ hỗn độn này.</t>
+          <t>À, cậu đây rồi! Ta phải cảm ơn cậu vì đã giúp chúng ta dọn dẹp mớ hỗn độn này.</t>
         </is>
       </c>
     </row>
@@ -8208,7 +8208,7 @@
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>Cậu đang chặn những mảnh giấc mơ à?</t>
+          <t>Cậu vừa chặn những mảnh giấc mơ đó à?</t>
         </is>
       </c>
     </row>
@@ -8273,7 +8273,7 @@
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>Đúng vậy. Những khối mộng tưởng ấy đã vỡ ra thành vô số mảnh mộng tưởng.</t>
+          <t>Chuẩn xác. Những khối mộng ấy đã vỡ ra thành vô số mảnh giấc mơ.</t>
         </is>
       </c>
     </row>
@@ -8338,7 +8338,7 @@
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>Chúng chạy tán loạn như lá trong rừng, khó mà thu thập hết.</t>
+          <t>Chúng chạy tán loạn như lá rụng trong rừng, khó mà thu thập hết được.</t>
         </is>
       </c>
     </row>
@@ -8403,7 +8403,7 @@
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>Ebony Gatekeeper có nhắc là ông ấy đang tìm cách giải quyết.</t>
+          <t>Ebony Gatekeeper bảo anh ấy đang tìm cách giải quyết.</t>
         </is>
       </c>
     </row>
@@ -8468,7 +8468,7 @@
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>Vậy à? Chà, có lẽ hắn sẽ phù hợp với nhiệm vụ này hơn ta...</t>
+          <t>Vậy à? Ừm, chắc hẳn cậu ấy sẽ phù hợp với nhiệm vụ này hơn tao...</t>
         </is>
       </c>
     </row>
@@ -8533,7 +8533,7 @@
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>Dreamwalker, tôi có việc muốn nhờ. Bạn có thể tiếp tục khôi phục những Vùng Ký Ức hỗn loạn đó không?</t>
+          <t>Người Du Hành Giấc Mơ à, ta có việc muốn nhờ cậy. Ngươi có thể tiếp tục khôi phục những Khu Vực Ký Ức hỗn loạn này không?</t>
         </is>
       </c>
     </row>
@@ -8598,7 +8598,7 @@
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>Cần phải hỏi sao?</t>
+          <t>Còn cần phải hỏi sao?</t>
         </is>
       </c>
     </row>
@@ -8663,7 +8663,7 @@
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>Được thôi, miễn là bạn trả tiền cho tôi.</t>
+          <t>Được thôi, miễn là cậu trả tiền cho tao.</t>
         </is>
       </c>
     </row>
@@ -8728,7 +8728,7 @@
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>Haha, tớ biết cậu sẽ nói vậy! Cảm ơn nhé. Và như mọi khi, tớ sẽ luôn ở đây nếu cậu cần gì đó.</t>
+          <t>Haha, tao biết cậu sẽ nói thế! Cảm ơn nhé. Và như mọi khi, nếu cần gì, cứ gọi tao.</t>
         </is>
       </c>
     </row>
@@ -8793,7 +8793,7 @@
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>Yên tâm đi. Somnoire luôn hào phóng mà. Và như mọi khi, tôi sẽ ở đây nếu bạn cần gì từ tôi.</t>
+          <t>Yên tâm nhé. Somnoire lúc nào cũng hào phóng mà. Và như mọi khi, nếu cậu cần gì, tớ luôn ở đây.</t>
         </is>
       </c>
     </row>
@@ -8858,7 +8858,7 @@
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>Cảnh vật quen thuộc, nhưng chẳng còn vẻ huy hoàng...</t>
+          <t>Một khung cảnh quen thuộc, nhưng đã mất đi vẻ lấp lánh...</t>
         </is>
       </c>
     </row>
@@ -8988,7 +8988,7 @@
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>Hừm... Tiếc thật. Như thế này vẫn chưa đủ cho cuốn sách tranh này...</t>
+          <t>Thở dài. Thật đáng tiếc... Chừng này vẫn còn quá ít cho cuốn sách ảnh này...</t>
         </is>
       </c>
     </row>
@@ -9053,7 +9053,7 @@
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>Để làm gì?</t>
+          <t>Dùng để làm gì?</t>
         </is>
       </c>
     </row>
@@ -9118,7 +9118,7 @@
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>Ồ, là cậu à, {PlayerName}. Chào mừng đến với thế giới của những khám phá và điều kỳ diệu!</t>
+          <t>Ồ, là cậu, {PlayerName}. Chúc chúng ta khám phá được thật nhiều điều kỳ diệu!</t>
         </is>
       </c>
     </row>
@@ -9183,7 +9183,7 @@
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>Cậu thấy thế nào? Mặc dù chưa có màu sắc gì, nhưng riêng bản phác thảo đã rất xuất sắc rồi!</t>
+          <t>Cậu thấy sao? Màu sắc thì chưa có, nhưng riêng những nét phác thảo đã rất phi thường rồi!</t>
         </is>
       </c>
     </row>
@@ -9313,7 +9313,7 @@
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>Tôi nhặt được nó từ một thương nhân gặp trên phố. Theo ông ấy, cuốn sách này có tiềm năng trở thành một kiệt tác.</t>
+          <t>Tôi mua được cuốn sách này từ một thương nhân trên phố. Theo ông ấy, cuốn sách này có tiềm năng trở thành một kiệt tác.</t>
         </is>
       </c>
     </row>
@@ -9378,7 +9378,7 @@
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>Nhưng họa sĩ lâm bệnh nặng và qua đời trước khi kịp tô màu. Không ai muốn trả tiền cho thứ chưa hoàn thiện cả.</t>
+          <t>Nhưng họa sĩ ấy lâm bệnh nặng và qua đời trước khi kịp tô màu. Chẳng ai muốn trả tiền cho một tác phẩm dở dang cả.</t>
         </is>
       </c>
     </row>
@@ -9443,7 +9443,7 @@
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>Bạn đã tìm thấy chưa?</t>
+          <t>Ngươi đã tìm được cái nào chưa?</t>
         </is>
       </c>
     </row>
@@ -9508,7 +9508,7 @@
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>Nghe có vẻ là kế hoạch hay.</t>
+          <t>Nghe có vẻ là kế hoạch tốt đấy.</t>
         </is>
       </c>
     </row>
@@ -9573,7 +9573,7 @@
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>Không, vẫn chưa. Nhưng trước đó, tôi phải giải quyết một chuyện trước đã. Cậu còn nhớ Overflowing Palette không?</t>
+          <t>Chưa, vẫn chưa. Nhưng trước đó, ta còn một việc phải làm. Cậu còn nhớ Bảng Màu Tràn Không?</t>
         </is>
       </c>
     </row>
@@ -9638,7 +9638,7 @@
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>Là một người quan sát, tôi sẽ tìm cách để tiếp tục dòng chảy cuộc sống của cuốn sách.</t>
+          <t>Thì, với tư cách là người quan sát, ta sẽ tìm cách để tiếp tục dòng chảy cuộc sống trong cuốn sách.</t>
         </is>
       </c>
     </row>
@@ -9703,7 +9703,7 @@
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>Nhưng trước khi tìm được họa sĩ này, tôi còn một việc phải giải quyết trước. Cậu còn nhớ Overflowing Palette không?</t>
+          <t>Nhưng trước khi tìm được họa sĩ này, tôi còn một việc phải giải quyết trước. Cậu còn nhớ Bảng Màu Tràn Đầy không?</t>
         </is>
       </c>
     </row>
@@ -9768,7 +9768,7 @@
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>Bảng Màu Tràn có thể ảnh hưởng đến màu sắc xung quanh, khiến chúng phai mờ trong thực tại.</t>
+          <t>Bảng Màu Tràn có thể ảnh hưởng đến màu sắc xung quanh, khiến chúng phai nhạt trong thực tại.</t>
         </is>
       </c>
     </row>
@@ -9898,7 +9898,7 @@
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>Tính cả tôi vào nhóm quan sát viên đó.</t>
+          <t>Tao cũng muốn vào băng quan sát viên đấy.</t>
         </is>
       </c>
     </row>
@@ -9963,7 +9963,7 @@
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>Thật sao? Ồ, điều đó có ý nghĩa rất lớn với tôi, {PlayerName}! Vậy thì tôi sẽ giao nhiệm vụ khôi phục các Faded Zone cho cậu.</t>
+          <t>Thật sao? Ồ, điều đó có ý nghĩa rất lớn với mình đấy, {PlayerName}! Vậy thì mình sẽ giao nhiệm vụ khôi phục các Vùng Đất Phai Mờ cho cậu.</t>
         </is>
       </c>
     </row>
@@ -10028,7 +10028,7 @@
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t>Mình sẽ tổng hợp danh sách các Faded Zone và gửi cho bạn sớm.</t>
+          <t>Mình sẽ tổng hợp danh sách các Tổ Tacet Đã Mờ và gửi cho cậu sớm thôi.</t>
         </is>
       </c>
     </row>
@@ -10093,7 +10093,7 @@
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>Chúc bạn khám phá thật nhiều điều kỳ diệu trên thế giới này.</t>
+          <t>Chào đón một thế giới đầy khám phá và kỳ diệu.</t>
         </is>
       </c>
     </row>
@@ -10158,7 +10158,7 @@
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t>Điều gì khiến cậu gia nhập Pioneer Association?</t>
+          <t>Điều gì đã khiến cậu gia nhập Hiệp hội Tiên phong?</t>
         </is>
       </c>
     </row>
@@ -10223,7 +10223,7 @@
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t>Về "cuốn sách tranh" ấy.</t>
+          <t>Về cuốn "sách tranh" ấy.</t>
         </is>
       </c>
     </row>
@@ -10288,7 +10288,7 @@
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>Tại sao tôi lại gia nhập Hiệp Hội Pioneer? Tất nhiên là vì tò mò. Tôi vẫn còn nhớ những dòng chữ viết trên bìa trong cuốn &lt;i&gt;Wutherium Geographic&lt;/i&gt;.</t>
+          <t>Sao mình lại gia nhập Hiệp Hội Tiên Phong? Tất nhiên là vì tò mò rồi. Mình vẫn nhớ rõ dòng chữ viết trên bìa trong cuốn &lt;i&gt;Wutherium Geographic&lt;/i&gt;.</t>
         </is>
       </c>
     </row>
@@ -10353,7 +10353,7 @@
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>"Hãy đi khám phá thế giới và chứng kiến lịch sử đang được tạo ra. Hãy chiêm ngưỡng những kiệt tác của nhân loại—nghệ thuật, công trình, những sáng tạo của chúng ta. Hãy nhìn ngắm tất cả, và cảm nhận tất cả."</t>
+          <t>"Hãy đi khắp thế gian và chứng kiến lịch sử đang được viết nên. Hãy chiêm ngưỡng những kiệt tác của nhân loại—nghệ thuật, công trình, những sáng tạo của chúng ta. Hãy nhìn thấy tất cả, và cảm nhận tất cả."</t>
         </is>
       </c>
     </row>
@@ -10418,7 +10418,7 @@
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>Tôi muốn phóng tầm mắt ra xa hơn nơi thân thể có thể đến.</t>
+          <t>Ta muốn phóng tầm mắt xa hơn nơi thân thể này có thể đến.</t>
         </is>
       </c>
     </row>
@@ -10483,7 +10483,7 @@
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>Yes. Sau khi mỗi Faded Zone được khôi phục, chúng ta chỉ cần tìm một nghệ nhân đáng tin cậy để tô màu lên thôi.</t>
+          <t>Đúng vậy. Sau khi mỗi Vùng Phai Màu được khôi phục, chỉ cần tìm một nghệ nhân đáng tin cậy để tô màu là xong.</t>
         </is>
       </c>
     </row>
@@ -10548,7 +10548,7 @@
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>Nói về nghệ sĩ, {PlayerName} có nghĩ đến ai không?</t>
+          <t>Nói về nghệ sĩ, cậu có nghĩ đến ai không, {PlayerName}?</t>
         </is>
       </c>
     </row>
@@ -10613,7 +10613,7 @@
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t>Tôi có một người bạn nghệ sĩ ở Jinzhou.</t>
+          <t>Tôi có quen một người bạn nghệ sĩ ở Jinzhou.</t>
         </is>
       </c>
     </row>
@@ -10678,7 +10678,7 @@
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t>Tuyệt quá. Nếu có cơ hội, bạn giới thiệu tôi với bạn của bạn nhé?</t>
+          <t>Tốt lắm. Khi nào có dịp, giới thiệu bạn cậu cho tôi nhé?</t>
         </is>
       </c>
     </row>
@@ -10743,7 +10743,7 @@
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>Cuối cùng chúng ta đã kết nối được rồi, {PlayerName}. Cậu có nghe thấy tôi không?</t>
+          <t>Cuối cùng chúng ta cũng kết nối được rồi, {PlayerName}. Cậu nghe thấy tao chứ?</t>
         </is>
       </c>
     </row>
@@ -10808,7 +10808,7 @@
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>(Cảm giác này là gì... phải chăng là... Somnoire?)</t>
+          <t>("Cảm giác này là gì... Phải chăng là... Somnoire?")</t>
         </is>
       </c>
     </row>
@@ -10873,7 +10873,7 @@
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>Đừng lo, chỉ là tôi thôi, Cat Trắng đến từ Somnoire. Tôi liên lạc với cậu qua giấc mơ...</t>
+          <t>Đừng lo, chỉ là ta thôi, Mèo Trắng từ Somnoire. Ta đang liên lạc với cậu qua giấc mơ đấy...</t>
         </is>
       </c>
     </row>
@@ -10938,7 +10938,7 @@
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>Có vài chuyện nên nói chuyện trực tiếp. Bạn có thể đến Thành Ragunna khi rảnh không? Mình cần bạn giúp một việc, meo...</t>
+          <t>Có những chuyện chỉ nên nói trực tiếp. Nếu có thời gian, cậu có thể đến Thành phố Ragunna không? Ta cần cậu giúp một việc, meo~</t>
         </is>
       </c>
     </row>
@@ -11003,7 +11003,7 @@
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>Hello, {PlayerName}... Thành phố này thật kỳ lạ, meo. Thú thật, đây là lần đầu tớ đến Ragunna.</t>
+          <t>Chào cậu, {PlayerName}... Thành phố này thật kỳ lạ, meo meo. Thú thật, đây là lần đầu tớ đến Ragunna.</t>
         </is>
       </c>
     </row>
@@ -11068,7 +11068,7 @@
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t>Meow?</t>
+          <t>Meo?</t>
         </is>
       </c>
     </row>
@@ -11133,7 +11133,7 @@
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t>Bạn là một con mèo...</t>
+          <t>Ngươi là một con mèo...</t>
         </is>
       </c>
     </row>
@@ -11198,7 +11198,7 @@
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>Hừm... thôi bỏ đi. Lý do tôi liên lạc với cậu, {PlayerName}, là vì tôi cảm nhận được tần số của cậu đến từ Ragunna.</t>
+          <t>Ơ... thôi kệ. Lý do tớ liên lạc với cậu, {PlayerName}, là vì tớ cảm nhận được tần số của cậu từ Ragunna.</t>
         </is>
       </c>
     </row>
@@ -11263,7 +11263,7 @@
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t>Ta đâu phải mèo tầm thường! Thôi, gác chuyện đó lại đã. Lý do thật sự ta liên lạc với {PlayerName} là vì ta cảm nhận được tần số của cậu từ Ragunna.</t>
+          <t>Ta đâu phải mèo tầm thường! À... thôi bỏ qua chuyện đó đã. Lý do thật sự ta liên lạc với cậu, {PlayerName}, là vì ta cảm nhận được tần số của cậu từ Ragunna.</t>
         </is>
       </c>
     </row>
@@ -11328,7 +11328,7 @@
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>Những node thử thách đặc biệt đó à?</t>
+          <t>Những nút thử thách đặc biệt đó à?</t>
         </is>
       </c>
     </row>
@@ -11393,7 +11393,7 @@
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>Kể từ sự cố lần trước, tôi đã nghiên cứu Somnoire, cố gắng khôi phục nhiệm vụ sao lưu giấc mơ.</t>
+          <t>Kể từ sự cố lần trước, tôi đã miệt mài nghiên cứu Somnoire, cố gắng khôi phục nhiệm vụ sao lưu giấc mơ.</t>
         </is>
       </c>
     </row>
@@ -11458,7 +11458,7 @@
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t>Nhưng tôi hoàn toàn bất lực trước những giấc mơ của Ragunna. Vì vậy, tôi muốn nhờ bạn tiếp tục hoàn thành những thử thách đó, {PlayerName}.</t>
+          <t>Nhưng trước những giấc mơ của Ragunna, ta hoàn toàn bất lực. Vậy nên, ta muốn nhờ cậu tiếp tục hoàn thành những thử thách đó, {PlayerName}.</t>
         </is>
       </c>
     </row>
@@ -11523,7 +11523,7 @@
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t>Tuy nhiên, tại Fagaceae Peninsula và Penitent's End, các Nút Mộng Cảnh dường như bị che phủ bởi một thế lực bí ẩn.</t>
+          <t>Tuy nhiên, tại Bán đảo Fagaceae và Penitent's End, các Nút Dreamscape dường như bị che phủ bởi một thế lực bí ẩn.</t>
         </is>
       </c>
     </row>
@@ -11653,7 +11653,7 @@
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t>Để kết nối hoàn toàn các Nút Giấc Mơ, cần loại bỏ những chướng ngại vật này. Hoàn thành thử thách, và tôi sẽ thưởng cho bạn xứng đáng, meo.</t>
+          <t>Để kết nối hoàn toàn các Nút Giấc Mơ, chúng ta phải dọn sạch những chướng ngại này. Hoàn thành thử thách đi, ta sẽ thưởng xứng đáng cho ngươi, meo~.</t>
         </is>
       </c>
     </row>
@@ -11718,7 +11718,7 @@
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t>Tôi sẽ suy nghĩ về chuyện đó.</t>
+          <t>Ta sẽ suy nghĩ về chuyện này.</t>
         </is>
       </c>
     </row>
@@ -11783,7 +11783,7 @@
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t>Được rồi. Tôi sẽ đánh dấu vị trí. Phải trông cậy vào bạn rồi, {PlayerName}.</t>
+          <t>Được rồi, tôi sẽ đánh dấu vị trí. Tôi trông cậy vào cậu đấy, {PlayerName}.</t>
         </is>
       </c>
     </row>
@@ -11848,7 +11848,7 @@
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t>Ra là vậy... thì ra đó là thứ ẩn nấp sâu trong mạng lưới Nút Giấc Mơ.</t>
+          <t>Ta thấy... vậy đó chính là thứ ẩn nấp sâu trong mạng lưới Nút Giấc Mơ.</t>
         </is>
       </c>
     </row>
@@ -11913,7 +11913,7 @@
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t>Có thứ gì đó đang tích cực thu thập những cơn ác mộng và cảm xúc tiêu cực của mọi người...</t>
+          <t>Có thứ gì đó đang thu thập những cơn ác mộng và cảm xúc tiêu cực của con người...</t>
         </is>
       </c>
     </row>
@@ -11978,7 +11978,7 @@
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t>Well done, {PlayerName}. Hiện tại, kết nối Somnoire đã có tiến triển. Chúng ta hãy thảo luận thêm khi gặp mặt nhé.</t>
+          <t>Làm tốt lắm, {PlayerName}. Hiện tại, kết nối với Somnoire đã có tiến triển rồi. Chúng ta hãy thảo luận kỹ hơn khi gặp mặt nhé.</t>
         </is>
       </c>
     </row>
@@ -12043,7 +12043,7 @@
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t>{PlayerName}, cậu có nghĩ rằng TD đặc biệt này giống với một số mảnh ký ức trong Somnoire không?</t>
+          <t>{PlayerName}, cậu có nghĩ Tổ Tacet đặc biệt này giống với vài mảnh ký ức trong Somnoire không?</t>
         </is>
       </c>
     </row>
@@ -12108,7 +12108,7 @@
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t>Có vài điểm tương đồng.</t>
+          <t>Có vài điểm giống nhau.</t>
         </is>
       </c>
     </row>
@@ -12173,7 +12173,7 @@
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t>Và điều đó khiến ta nhớ đến một người quen cũ...</t>
+          <t>Và điều đó khiến tao nhớ tới một người quen cũ...</t>
         </is>
       </c>
     </row>
@@ -12238,7 +12238,7 @@
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t>Đúng vậy, nếu nhìn kỹ, nó rất giống với những giấc mơ bị tha hóa kia.</t>
+          <t>Đúng vậy, nếu nhìn kỹ, nó rất giống với những giấc mơ bị tha hóa đó.</t>
         </is>
       </c>
     </row>
@@ -12303,7 +12303,7 @@
       </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t>Tôi đang nói về những giấc mơ bị tha hóa ấy, meo.</t>
+          <t>Tao đang nói về những giấc mơ bị tha hóa ấy, meo~</t>
         </is>
       </c>
     </row>
@@ -12368,7 +12368,7 @@
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t>Giấc mơ là những ảo ảnh từ tiềm thức. Dù chúng hóa thành những mảnh ký ức, chúng vẫn mang theo mọi niềm vui và nỗi buồn của người mơ.</t>
+          <t>Giấc mơ là những hình ảnh từ tiềm thức. Dù chúng hóa thành những mảnh ký ức, chúng vẫn mang theo mọi niềm vui và nỗi buồn của kẻ mơ.</t>
         </is>
       </c>
     </row>
@@ -12433,7 +12433,7 @@
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t>Nhưng những TD đặc biệt đó... như thể tiềm thức của mọi người đã được thống nhất bởi một khái niệm duy nhất, chỉ mang theo một khát khao.</t>
+          <t>Nhưng những Tổ Tacet đặc biệt đó... cứ như thể tiềm thức của mọi người bị thống nhất bởi một khái niệm duy nhất, chỉ mang theo một khát khao duy nhất.</t>
         </is>
       </c>
     </row>
@@ -12563,7 +12563,7 @@
       </c>
       <c r="M185" t="inlineStr">
         <is>
-          <t>Tôi đã thấy một vực thẳm đen ngòm, nơi mọi người xếp hàng ngay ngắn, bò trườn, thực hiện những cử chỉ giống nhau, lẩm bẩm những lời giống nhau, mắc kẹt trong cùng một giấc mơ.</t>
+          <t>Ta đã thấy một vực thẳm đen ngòm, nơi mọi người xếp hàng ngay ngắn, bò lết, lặp đi lặp lại cùng một động tác, thì thầm cùng một câu, mắc kẹt trong cùng một giấc mơ.</t>
         </is>
       </c>
     </row>
@@ -12628,7 +12628,7 @@
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t>Ngay sau đó, họ nhận ra sự hiện diện của tôi và quay lại nhìn tôi... Đôi mắt họ... Đồng tử của họ bị nhuốm cùng một thứ chất đó...</t>
+          <t>Khoảnh khắc sau đó, chúng nhận ra sự hiện diện của ta và quay lại nhìn thẳng vào mắt ta... Đôi mắt ấy... Đồng tử của chúng bị nhuốm cùng một thứ chất lạ...</t>
         </is>
       </c>
     </row>
@@ -12693,7 +12693,7 @@
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t>Và trong bóng tối phía sau họ, một đôi mắt khổng lồ từ từ mở ra... Ta chưa từng thấy một giấc mơ như thế này bao giờ.</t>
+          <t>Và trong bóng tối phía sau họ, một đôi mắt khổng lồ từ từ mở ra… Tớ chưa bao giờ thấy một giấc mơ kỳ lạ như thế này.</t>
         </is>
       </c>
     </row>
@@ -12758,7 +12758,7 @@
       </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t>Nghe có vẻ không ổn...</t>
+          <t>Nghe... không yên tâm chút nào.</t>
         </is>
       </c>
     </row>
@@ -12823,7 +12823,7 @@
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t>Tất cả bọn họ đều quay lại nhìn bạn sao?</t>
+          <t>Họ đều quay sang nhìn cậu à?</t>
         </is>
       </c>
     </row>
@@ -12888,7 +12888,7 @@
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t>Yes. Chỉ nghĩ đến thôi đã thấy khó chịu rồi.</t>
+          <t>Đúng vậy. Chỉ nghĩ đến thôi đã thấy bất an rồi.</t>
         </is>
       </c>
     </row>
@@ -12953,7 +12953,7 @@
       </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t>Chuyện đó không bình thường chút nào, meo... Chỉ nghĩ đến thôi là mình đã thấy bất an rồi.</t>
+          <t>Không bình thường chút nào, meo... Chỉ nghĩ đến thôi đã thấy khó chịu rồi.</t>
         </is>
       </c>
     </row>
@@ -13018,7 +13018,7 @@
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t>{PlayerName} à, tôi muốn nhờ cậu tiếp tục tiêu diệt những TD ẩn nấp trong mạng lưới. Chỉ như vậy, những giấc mơ trong Somnoire mới được an toàn.</t>
+          <t>Vậy nên, {PlayerName}, tớ muốn nhờ cậu tiếp tục tiêu diệt những Tacet Discord ẩn nấp trong mạng lưới. Chỉ có vậy, những giấc mơ lưu giữ trong Somnoire mới được an toàn.</t>
         </is>
       </c>
     </row>
@@ -13083,7 +13083,7 @@
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t>Well done, {PlayerName}. Ta có thể cảm nhận được tất cả các Nút Mộng Cảnh giờ đã được kết nối.</t>
+          <t>Làm tốt lắm, {PlayerName}. Tao có thể cảm nhận được tất cả các Nút Dreamscape đã được kết nối rồi.</t>
         </is>
       </c>
     </row>
@@ -13148,7 +13148,7 @@
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t>Mối đe dọa tiềm ẩn đã được dọn sạch... Ta đã chuẩn bị phần thưởng cho ngươi rồi, meo. Hãy gặp nhau trực tiếp để bàn chi tiết nhé.</t>
+          <t>Mối đe dọa ẩn giấu đã được dọn sạch... Ta đã chuẩn bị phần thưởng cho ngươi rồi, meo. Hãy gặp mặt trực tiếp để bàn chi tiết.</t>
         </is>
       </c>
     </row>
@@ -13213,7 +13213,7 @@
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t>Làm tốt lắm, {PlayerName}! Tôi biết bạn có thể làm được mà.</t>
+          <t>Làm tốt lắm, {PlayerName}! Tao biết cậu làm được mà.</t>
         </is>
       </c>
     </row>
@@ -13278,7 +13278,7 @@
       </c>
       <c r="M196" t="inlineStr">
         <is>
-          <t>Giờ đây tần số giấc mơ ở khu vực Ragunna đã ổn định... Hmm, phải nói thế nào nhỉ... Cảm giác rất... Rinascita.</t>
+          <t>Giờ tần số giấc mơ ở khu vực Ragunna đã ổn định... Hmm, phải nói thế nào nhỉ... Cảm giác rất... Rinascita.</t>
         </is>
       </c>
     </row>
@@ -13343,7 +13343,7 @@
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t>Qua những giấc mơ này, có vẻ người dân Ragunna sống khá hạnh phúc... Vậy tại sao lại có một tiềm thức hỗn loạn ẩn giấu bên dưới như vậy?</t>
+          <t>Qua những giấc mơ này, có vẻ người dân Ragunna sống rất hạnh phúc... Vậy tại sao lại có một tiềm thức hỗn loạn như vậy ẩn sâu bên dưới?</t>
         </is>
       </c>
     </row>
@@ -13408,7 +13408,7 @@
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t>Gần đây truyện quái vật biển sâu có phổ biến không?</t>
+          <t>Dạo này chuyện quái vật biển sâu có đang thịnh hành không?</t>
         </is>
       </c>
     </row>
@@ -13473,7 +13473,7 @@
       </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t>Có lẽ Tổ Chức đang che giấu điều gì đó...</t>
+          <t>Có lẽ Hội Ánh Sáng đang che giấu điều gì đó...</t>
         </is>
       </c>
     </row>
@@ -13538,7 +13538,7 @@
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t>Tớ thật sự không hiểu, meo, sao lại có người thích những thứ đáng sợ như thế chứ?! Biển sâu tối om, mà tớ còn chẳng biết bơi, meo.</t>
+          <t>Mình thực sự chẳng hiểu nổi, meo à, sao lại có người thích những thứ đáng sợ như thế nhỉ?! Biển sâu tối om om thế này, mà mình còn chẳng biết bơi cơ, meo...</t>
         </is>
       </c>
     </row>
@@ -13603,7 +13603,7 @@
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t>Tôi không chắc lắm... nhưng trong những mẫu này, giấc mơ của các thành viên Order lại ít đến bất ngờ... Chuyện gì đang xảy ra vậy?</t>
+          <t>Tôi không chắc lắm... nhưng trong những mẫu này, giấc mơ của các thành viên Hội Ánh Sáng lại ít đến bất ngờ... Chuyện gì đang xảy ra vậy?</t>
         </is>
       </c>
     </row>
@@ -13668,7 +13668,7 @@
       </c>
       <c r="M202" t="inlineStr">
         <is>
-          <t>Để chuyện đó lại sau đi. Đến lúc đó, Somnoire ở Ragunna sẽ được thành lập hoàn chỉnh.</t>
+          <t>Để chuyện đó lại sau. Đến lúc đó, Somnoire ở Ragunna sẽ được thiết lập hoàn chỉnh.</t>
         </is>
       </c>
     </row>
@@ -13733,7 +13733,7 @@
       </c>
       <c r="M203" t="inlineStr">
         <is>
-          <t>Một lần nữa cảm ơn {PlayerName} vì tất cả sự giúp đỡ của bạn. Nhân tiện, ngoài phần thưởng đã thỏa thuận, tôi muốn tặng bạn món này làm kỷ vật.</t>
+          <t>Một lần nữa cảm ơn cậu đã giúp đỡ, {PlayerName}. Nhân tiện, ngoài phần thưởng đã thỏa thuận, mình muốn tặng cậu món này làm kỷ vật.</t>
         </is>
       </c>
     </row>
@@ -13798,7 +13798,7 @@
       </c>
       <c r="M204" t="inlineStr">
         <is>
-          <t>Cái gì đây?</t>
+          <t>Đây là cái gì?</t>
         </is>
       </c>
     </row>
@@ -13863,7 +13863,7 @@
       </c>
       <c r="M205" t="inlineStr">
         <is>
-          <t>Đây là một mẫu vật độc đáo tôi tìm thấy trong Nút Giấc Mơ. Tôi chưa rõ nó dùng để làm gì, nhưng trông chắc chắn rất tinh xảo.</t>
+          <t>Đây là một mẫu vật đặc biệt mà ta tìm thấy trong một Nút Mộng Cảnh. Ta chưa rõ nó dùng để làm gì, nhưng chắc chắn là rất tinh xảo.</t>
         </is>
       </c>
     </row>
@@ -13993,7 +13993,7 @@
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t>{PlayerName}, ta có thể cảm nhận sương mù biển trên hòn đảo này đang tan dần.</t>
+          <t>{PlayerName}, ta cảm nhận được sương mù trên hòn đảo này đang dần tan đi.</t>
         </is>
       </c>
     </row>
@@ -14058,7 +14058,7 @@
       </c>
       <c r="M208" t="inlineStr">
         <is>
-          <t>Dù vẫn chưa ổn định, nhưng các Nút Dreamscape ở đây giờ đã có thể truy cập được rồi, meo.</t>
+          <t>Dù vẫn chưa ổn định, nhưng các Dreamscape Node ở đây giờ đã có thể truy cập được rồi, meo~</t>
         </is>
       </c>
     </row>
@@ -14123,7 +14123,7 @@
       </c>
       <c r="M209" t="inlineStr">
         <is>
-          <t>Vậy là Dreamscape Nexus đã bị chiếm bởi những TD ám ảnh này...</t>
+          <t>Vậy là Dreamscape Nexus đã bị những TD ám ảnh này chiếm giữ...</t>
         </is>
       </c>
     </row>
@@ -14188,7 +14188,7 @@
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t>Hiện tại trung tâm dường như đã kết nối lại với mạng lưới giấc mơ, {PlayerName}. Bạn có thể thử kết nối với nó, meo~.</t>
+          <t>Giờ trung tâm dường như đã kết nối lại với mạng lưới giấc mơ rồi, {PlayerName}. Cậu có thể thử kết nối với nó đấy, meo.</t>
         </is>
       </c>
     </row>
@@ -14253,7 +14253,7 @@
       </c>
       <c r="M211" t="inlineStr">
         <is>
-          <t>Ôi... tri kỷ của tôi, vị vua của nguồn cảm hứng... chuyện gì đã xảy ra với anh thế...</t>
+          <t>Ồ... tri kỷ của ta, vị vua của cảm hứng... ngươi đã ra sao rồi...</t>
         </is>
       </c>
     </row>
@@ -14318,7 +14318,7 @@
       </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t>*Buzz—buzz—whirr—clickety-clack—*</t>
+          <t>*Vù vù—rè rè—lạch cạch—*</t>
         </is>
       </c>
     </row>
@@ -14383,7 +14383,7 @@
       </c>
       <c r="M213" t="inlineStr">
         <is>
-          <t>Ôi... tri kỷ của tôi, vị vua của nguồn cảm hứng... chuyện gì đã xảy ra với anh thế...</t>
+          <t>Ồ... tri kỷ của ta, vị vua của cảm hứng... ngươi đã ra sao rồi...</t>
         </is>
       </c>
     </row>
@@ -14448,7 +14448,7 @@
       </c>
       <c r="M214" t="inlineStr">
         <is>
-          <t>*Buzz—buzz—whirr—clickety-clack—*</t>
+          <t>*Vù vù—rè rè—lạch cạch—*</t>
         </is>
       </c>
     </row>
@@ -14513,7 +14513,7 @@
       </c>
       <c r="M215" t="inlineStr">
         <is>
-          <t>Echo này có vấn đề gì vậy?</t>
+          <t>Echo này bị sao thế?</t>
         </is>
       </c>
     </row>
@@ -14643,7 +14643,7 @@
       </c>
       <c r="M217" t="inlineStr">
         <is>
-          <t>Hello, lữ khách từ phương xa. Tôi là Tommaso, một nhạc sĩ. Đây là Echo đồng hành của tôi, Melody "Aria Mummer".</t>
+          <t>Xin chào, lữ khách phương xa. Ta là Tommaso, một nhạc sĩ. Đây là bạn đồng hành Echo của ta, giai điệu "Aria Mummer".</t>
         </is>
       </c>
     </row>
@@ -14708,7 +14708,7 @@
       </c>
       <c r="M218" t="inlineStr">
         <is>
-          <t>Melody có khả năng ghi lại mọi giai điệu nó nghe thấy và điều khiển "Dàn Nhạc Melody" xung quanh để tái hiện lại chúng.</t>
+          <t>Melody có khả năng ghi lại mọi giai điệu nó nghe được và điều khiển "Dàn Nhạc Melody" xung quanh tái hiện lại chúng.</t>
         </is>
       </c>
     </row>
@@ -14773,7 +14773,7 @@
       </c>
       <c r="M219" t="inlineStr">
         <is>
-          <t>Khi tôi hoàn thành công việc thì Melody đã trở nên như thế này rồi...</t>
+          <t>Lúc tao vừa hoàn thành xong công việc, Melody đã thành ra thế này rồi...</t>
         </is>
       </c>
     </row>
@@ -14838,7 +14838,7 @@
       </c>
       <c r="M220" t="inlineStr">
         <is>
-          <t>*Reng—reng reng—rên rỉ—*</t>
+          <t>*Vù vù—rên rỉ—*</t>
         </is>
       </c>
     </row>
@@ -14903,7 +14903,7 @@
       </c>
       <c r="M221" t="inlineStr">
         <is>
-          <t>Nó không còn thể trình diễn toàn bộ bản nhạc nữa. Ngay cả giọng hát của nó cũng có dấu hiệu "méo mó"... Melody... nếu không có em, tôi phải sống sao đây?</t>
+          <t>Nó không còn chơi được những bản nhạc hoàn chỉnh nữa. Ngay cả giọng hát của nó cũng đã bắt đầu "méo mó"... Giai điệu ơi... nếu không có ngươi, ta biết phải sống sao đây?</t>
         </is>
       </c>
     </row>
@@ -14968,7 +14968,7 @@
       </c>
       <c r="M222" t="inlineStr">
         <is>
-          <t>Có lẽ là vì nó đã nghe quá nhiều thứ khác nhau...</t>
+          <t>Có lẽ vì nó đã nghe quá nhiều thứ khác nhau...</t>
         </is>
       </c>
     </row>
@@ -15033,7 +15033,7 @@
       </c>
       <c r="M223" t="inlineStr">
         <is>
-          <t>Chỉ làm việc không chơi sẽ khiến cả trí óc sắc bén nhất cũng trở nên mờ nhạt...</t>
+          <t>Làm việc không ngừng nghỉ sẽ khiến cả trí óc sắc bén nhất cũng trở nên cùn mòn...</t>
         </is>
       </c>
     </row>
@@ -15098,7 +15098,7 @@
       </c>
       <c r="M224" t="inlineStr">
         <is>
-          <t>Chắc vậy... Có vẻ khả thi... À, bạn tôi, nhìn dáng điệu và trang phục của cậu, chắc hẳn là một nhà thám hiểm dày dạn rồi.</t>
+          <t>Chắc chắn... có vẻ như vậy... À, bạn tôi ơi, nhìn dáng đi và bộ đồ của cậu, chắc hẳn là một nhà thám hiểm dày dạn kinh nghiệm rồi.</t>
         </is>
       </c>
     </row>
@@ -15163,7 +15163,7 @@
       </c>
       <c r="M225" t="inlineStr">
         <is>
-          <t>Bạn đã từng nghe hoặc ghi lại bản nhạc nào đặc biệt đáng nhớ trong chuyến phiêu lưu của mình chưa?</t>
+          <t>Trong chuyến phiêu lưu của mình, ngươi có nghe hoặc ghi lại bản nhạc nào đáng nhớ không?</t>
         </is>
       </c>
     </row>
@@ -15228,7 +15228,7 @@
       </c>
       <c r="M226" t="inlineStr">
         <is>
-          <t>Bạn có thể chia sẻ chúng với Melody không? Có thể sẽ làm dịu "triệu chứng" của nó...</t>
+          <t>Cậu đưa bản quy tắc này cho Melody được không? Có thể sẽ giúp giảm bớt "triệu chứng" của nó...</t>
         </is>
       </c>
     </row>
@@ -15293,7 +15293,7 @@
       </c>
       <c r="M227" t="inlineStr">
         <is>
-          <t>Bạn ơi, trong chuyến phiêu lưu của chúng ta, cậu đã từng nghe hoặc ghi lại bản nhạc nào để lại ấn tượng đặc biệt sâu sắc chưa?</t>
+          <t>Bạn ơi, trong suốt cuộc hành trình, cậu có từng nghe hay ghi lại bản nhạc nào để lại ấn tượng sâu sắc không?</t>
         </is>
       </c>
     </row>
@@ -15358,7 +15358,7 @@
       </c>
       <c r="M228" t="inlineStr">
         <is>
-          <t>Bạn có thể chia sẻ chúng với Melody không? Có thể sẽ làm dịu "triệu chứng" của nó...</t>
+          <t>Cậu đưa bản quy tắc này cho Melody được không? Có thể sẽ giúp giảm bớt "triệu chứng" của nó...</t>
         </is>
       </c>
     </row>
@@ -15423,7 +15423,7 @@
       </c>
       <c r="M229" t="inlineStr">
         <is>
-          <t>Ồ... ồ! Đúng rồi! Đây mới là âm thanh mà Melody đáng lẽ phải có! Đây... đây mới là âm nhạc thực sự!</t>
+          <t>Ồ... ôi! Đúng rồi! Đây mới là âm thanh mà Melody đáng có! Đây... đây mới là âm nhạc đích thực!</t>
         </is>
       </c>
     </row>
@@ -15488,7 +15488,7 @@
       </c>
       <c r="M230" t="inlineStr">
         <is>
-          <t>Cảm ơn! Lữ khách từ phương xa! Cái... "Hộp Nhạc" trong tay cậu này, cậu tìm thấy nó ở đâu thế? Âm nhạc kỳ diệu như vậy, lại được ghi trên một chiếc đĩa nhỏ bé thế này...</t>
+          <t>Cảm ơn cậu! Người lữ khách từ phương xa! Cái… "Hộp Nhạc" này trong tay cậu, cậu tìm thấy nó ở đâu thế? Âm nhạc tuyệt vời như vậy lại được lưu giữ trên một chiếc đĩa nhỏ bé này…</t>
         </is>
       </c>
     </row>
@@ -15553,7 +15553,7 @@
       </c>
       <c r="M231" t="inlineStr">
         <is>
-          <t>Chỉ là may mắn thôi.</t>
+          <t>Chỉ là một phen may mắn.</t>
         </is>
       </c>
     </row>
@@ -15618,7 +15618,7 @@
       </c>
       <c r="M232" t="inlineStr">
         <is>
-          <t>Chuyển thể từ *True Experiences*.</t>
+          <t>Chuyển thể từ Những Trải Nghiệm Chân Thực.</t>
         </is>
       </c>
     </row>
@@ -15683,7 +15683,7 @@
       </c>
       <c r="M233" t="inlineStr">
         <is>
-          <t>Ta chỉ là một người khuân vác ở thế giới này.</t>
+          <t>Ta chỉ là một kẻ khuân vác trong thế giới này thôi.</t>
         </is>
       </c>
     </row>
@@ -15748,7 +15748,7 @@
       </c>
       <c r="M234" t="inlineStr">
         <is>
-          <t>Có vẻ Melody và tôi nên rời khỏi Ragunna City để khám phá thế giới rộng lớn hơn.</t>
+          <t>Có vẻ như ta và Melody nên rời khỏi Ragunna City để khám phá thế giới rộng lớn ngoài kia.</t>
         </is>
       </c>
     </row>
@@ -15813,7 +15813,7 @@
       </c>
       <c r="M235" t="inlineStr">
         <is>
-          <t>Trong sự hỗn loạn của âm thanh thế gian, thách thức cả đời của mỗi nhạc sĩ là chắt lọc những giai điệu thuần khiết nhất... và "Người Diễn Aria" cũng không ngoại lệ.</t>
+          <t>Giữa muôn âm thanh hỗn độn của thế giới, thử thách muôn đời của mỗi nhạc sĩ là chắt lọc những giai điệu thuần khiết nhất... và "Aria Mummers" cũng không ngoại lệ.</t>
         </is>
       </c>
     </row>
@@ -15878,7 +15878,7 @@
       </c>
       <c r="M236" t="inlineStr">
         <is>
-          <t>Có lẽ tại Rinascita, bạn sẽ gặp những "Aria Mummers" khác. Họ có thể đang đối mặt với những thử thách tương tự.</t>
+          <t>Có thể ở Rinascita, cậu sẽ gặp những "Diễn Viên Aria" khác. Họ có thể cũng đang đối mặt với những thử thách tương tự.</t>
         </is>
       </c>
     </row>
@@ -15943,7 +15943,7 @@
       </c>
       <c r="M237" t="inlineStr">
         <is>
-          <t>Tôi luôn tin cùng Melody rằng âm nhạc tuyệt vời có sức mạnh lay động lòng người và truyền cảm hứng cho sự thay đổi.</t>
+          <t>Tôi vẫn luôn tin, cùng với Melody, rằng âm nhạc vĩ đại có sức mạnh lay động lòng người và truyền cảm hứng cho sự thay đổi.</t>
         </is>
       </c>
     </row>
@@ -16008,7 +16008,7 @@
       </c>
       <c r="M238" t="inlineStr">
         <is>
-          <t>Xin hãy nhận những món quà này như lời cảm ơn vì đã giúp đỡ tôi!</t>
+          <t>Hãy nhận lấy những thứ này như lời cảm ơn vì đã giúp đỡ tớ!</t>
         </is>
       </c>
     </row>
@@ -16073,7 +16073,7 @@
       </c>
       <c r="M239" t="inlineStr">
         <is>
-          <t>Trong cuộc phiêu lưu, nếu tình cờ thu thập được những "Melody Box" khác, hãy giúp đỡ các "Aria Mummer" khác nữa nhé.</t>
+          <t>Trong chuyến phiêu lưu của mình, nếu tình cờ thu thập được những "Hộp Nhạc Khúc" khác, xin hãy giúp đỡ luôn cả những "Diễn Viên Aria" khác nhé.</t>
         </is>
       </c>
     </row>
@@ -16138,7 +16138,7 @@
       </c>
       <c r="M240" t="inlineStr">
         <is>
-          <t>Tránh xa những bức tượng của ta nếu không muốn nếm mùi thất bại.</t>
+          <t>Tránh xa các bức tượng của ta nếu không muốn nếm mùi thất bại.</t>
         </is>
       </c>
     </row>
@@ -16203,7 +16203,7 @@
       </c>
       <c r="M241" t="inlineStr">
         <is>
-          <t>Cậu kia! Cho ta xem thực lực của cậu đi!</t>
+          <t>Mày! Cho tao thấy mày có gì trong người đi.</t>
         </is>
       </c>
     </row>
@@ -16268,7 +16268,7 @@
       </c>
       <c r="M242" t="inlineStr">
         <is>
-          <t>Ta đã thua rồi. Ta thật bất lực.</t>
+          <t>Ta đã bị áp đảo. Ta cúi mình nhận thua.</t>
         </is>
       </c>
     </row>
@@ -16333,7 +16333,7 @@
       </c>
       <c r="M243" t="inlineStr">
         <is>
-          <t>Chỉ có vậy thôi à?</t>
+          <t>Chỉ có vậy thôi sao?</t>
         </is>
       </c>
     </row>
@@ -16398,7 +16398,7 @@
       </c>
       <c r="M244" t="inlineStr">
         <is>
-          <t>Quay lại rồi à? Lấy cái này đi!</t>
+          <t>Muốn thêm à? Ăn đòn này đi!</t>
         </is>
       </c>
     </row>
@@ -16463,7 +16463,7 @@
       </c>
       <c r="M245" t="inlineStr">
         <is>
-          <t>Bíp... Những lá cờ vươn cao, chiến thắng luôn gọi tên! Những lá cờ vươn cao, chiến thắng luôn gọi tên! Bíp...</t>
+          <t>Bíp... Cờ phấp phới, chiến thắng luôn gọi tên! Cờ phấp phới, chiến thắng luôn gọi tên! Bíp...</t>
         </is>
       </c>
     </row>
@@ -16528,7 +16528,7 @@
       </c>
       <c r="M246" t="inlineStr">
         <is>
-          <t>Cái gì đây?</t>
+          <t>Cái gì vậy?</t>
         </is>
       </c>
     </row>
@@ -16593,7 +16593,7 @@
       </c>
       <c r="M247" t="inlineStr">
         <is>
-          <t>Nó bị hỏng à?</t>
+          <t>Nó đã hỏng rồi sao?</t>
         </is>
       </c>
     </row>
@@ -16658,7 +16658,7 @@
       </c>
       <c r="M248" t="inlineStr">
         <is>
-          <t>(Tìm hiểu xem nó muốn nói gì)</t>
+          <t>Cố hiểu xem nó đang muốn nói gì đã.</t>
         </is>
       </c>
     </row>
@@ -16723,7 +16723,7 @@
       </c>
       <c r="M249" t="inlineStr">
         <is>
-          <t>Đó là lý do chúng ta tổ chức một cuộc săn mô phỏng trong những khúc quanh hỗn loạn của Khu Phố Cũ đã cạn kiệt!</t>
+          <t>Chính vì thế mà chúng ta sẽ tổ chức một cuộc săn mô phỏng trong những ngõ ngách hỗn loạn của Khu Phố Cũ đã cạn nước!</t>
         </is>
       </c>
     </row>
@@ -16788,7 +16788,7 @@
       </c>
       <c r="M250" t="inlineStr">
         <is>
-          <t>Sẵn sàng chiến đấu chưa? Tim đập thình thịch, máu sôi lên nào? Hãy săn lùng những Tacet Discord, tích lũy điểm số và tiến vào vòng tiếp theo!</t>
+          <t>Ngươi đã sẵn sàng chiến đấu chưa? Tim đập thình thịch, máu sôi sục? Truy đuổi những Tacet Discord, tích lũy điểm số, rồi lao vào vòng kế tiếp!</t>
         </is>
       </c>
     </row>
@@ -16853,7 +16853,7 @@
       </c>
       <c r="M251" t="inlineStr">
         <is>
-          <t>Có phần thưởng không?</t>
+          <t>Có phần thưởng chứ?</t>
         </is>
       </c>
     </row>
@@ -16918,7 +16918,7 @@
       </c>
       <c r="M252" t="inlineStr">
         <is>
-          <t>Bíp... Đến nhận thưởng nào! Chiến thắng thuộc về bạn!</t>
+          <t>Bíp... Đến nhận phần thưởng của cậu đi! Chiến thắng thuộc về cậu rồi!</t>
         </is>
       </c>
     </row>
@@ -16983,7 +16983,7 @@
       </c>
       <c r="M253" t="inlineStr">
         <is>
-          <t>Bíp... Bạn đã chinh phục độ khó cao nhất thành công! Chiến thắng thuộc về bạn! Chiến thắng thuộc về bạn!</t>
+          <t>Bíp... Cậu đã chinh phục thành công độ khó cao nhất! Chiến thắng thuộc về cậu! Chiến thắng thuộc về cậu!</t>
         </is>
       </c>
     </row>
@@ -17048,7 +17048,7 @@
       </c>
       <c r="M254" t="inlineStr">
         <is>
-          <t>Bíp... Hoàn thành thử thách! Chiến thắng thuộc về bạn!</t>
+          <t>Bíp... Thử thách hoàn thành! Chiến thắng thuộc về cậu!</t>
         </is>
       </c>
     </row>
@@ -17113,7 +17113,7 @@
       </c>
       <c r="M255" t="inlineStr">
         <is>
-          <t>Bíp! Bạn là người chiến thắng cuối cùng! Xin chúc mừng!</t>
+          <t>Bíp! Người chiến thắng cuối cùng chính là cậu! Xin chúc mừng!</t>
         </is>
       </c>
     </row>
@@ -17178,7 +17178,7 @@
       </c>
       <c r="M256" t="inlineStr">
         <is>
-          <t>Chỉ có vậy thôi sao?</t>
+          <t>Thế là đến đây thôi sao?</t>
         </is>
       </c>
     </row>
@@ -17243,7 +17243,7 @@
       </c>
       <c r="M257" t="inlineStr">
         <is>
-          <t>Bíp... That's right! Bạn đã vượt qua thử thách và giành được sự tôn trọng của Banner of Conquest.</t>
+          <t>Bíp... Đúng vậy! Cậu đã vượt qua thử thách và giành được sự tôn trọng của Banner of Conquest.</t>
         </is>
       </c>
     </row>
@@ -17308,7 +17308,7 @@
       </c>
       <c r="M258" t="inlineStr">
         <is>
-          <t>Và giờ đây, cậu có thể nhận Phước Lành của các Biểu Ngữ.</t>
+          <t>Và giờ đây, ngươi có thể nhận Lời Ban Phước của Những Lá Cờ.</t>
         </is>
       </c>
     </row>
@@ -17373,7 +17373,7 @@
       </c>
       <c r="M259" t="inlineStr">
         <is>
-          <t>Hãy nhận lấy phước lành.</t>
+          <t>Đón nhận phước lành</t>
         </is>
       </c>
     </row>
@@ -17438,7 +17438,7 @@
       </c>
       <c r="M260" t="inlineStr">
         <is>
-          <t>Bạn nhắm mắt lại. Một lúc sau, bạn bắt đầu nghe thấy giọng Breen the Screen đầy háo hức.</t>
+          <t>Bạn nhắm mắt lại. Một lúc sau, giọng hào hứng của Breen the Screen vang lên bên tai.</t>
         </is>
       </c>
     </row>
@@ -17503,7 +17503,7 @@
       </c>
       <c r="M261" t="inlineStr">
         <is>
-          <t>Bíp... Hãy nhìn xem! Đây là Cờ Chinh Phục, do Ủy ban Septimont Agon cung cấp. Kích hoạt nó và nó sẽ giúp bạn quét sạch Tacet Discord!</t>
+          <t>Bíp... Hãy nhìn xem! Đây là Cờ Chinh Phục, do Ủy ban Septimont Agon cung cấp. Kích hoạt nó, và nó sẽ giúp cậu tiêu diệt các Tacet Discord!</t>
         </is>
       </c>
     </row>
@@ -17568,7 +17568,7 @@
       </c>
       <c r="M262" t="inlineStr">
         <is>
-          <t>Một tấm băng rôn lớn như thế này chỉ có thể kích hoạt khi không có Tacet Discord nào ở gần. Tất nhiên, nó sẽ mang lại hiệu ứng tăng cường mạnh hơn! Beep—</t>
+          <t>Một tấm biểu ngữ lớn như thế này chỉ có thể kích hoạt khi không có Tacet Discord nào ở gần. Tất nhiên, nó sẽ mang lại hiệu ứng tăng cường cực mạnh! Bíp—</t>
         </is>
       </c>
     </row>
@@ -17633,7 +17633,7 @@
       </c>
       <c r="M263" t="inlineStr">
         <is>
-          <t>Vậy, mục tiêu của chúng ta trong thử thách này là—</t>
+          <t>Vậy nên, trong thử thách này, mục tiêu của chúng ta là—</t>
         </is>
       </c>
     </row>
@@ -17698,7 +17698,7 @@
       </c>
       <c r="M264" t="inlineStr">
         <is>
-          <t>Đánh bại kẻ địch và giành chiến thắng.</t>
+          <t>Để đánh bại kẻ thù và giành lấy chiến thắng.</t>
         </is>
       </c>
     </row>
@@ -17763,7 +17763,7 @@
       </c>
       <c r="M265" t="inlineStr">
         <is>
-          <t>Để lấy lại biểu ngữ và giành lại các khu vực.</t>
+          <t>Để lấy lại biểu ngữ và giành lại những khu vực đó.</t>
         </is>
       </c>
     </row>
@@ -17828,7 +17828,7 @@
       </c>
       <c r="M266" t="inlineStr">
         <is>
-          <t>Đúng rồi! Cậu nắm bắt nhanh thật đấy! Tiến lên nào, Chiến Binh Dũng Cảm! Những lá cờ vẫn tung bay, chiến thắng luôn gọi tên! Mong cậu sẽ được đắm chìm trong những tiếng reo hò chiến thắng!</t>
+          <t>Đúng rồi! Cậu hiểu nhanh thật đấy! Tiến lên, Chiến Binh Dũng Cảm! Cờ phướn tung bay, chiến thắng đang gọi tên! Mong cậu được đắm chìm trong tiếng reo hò chiến thắng!</t>
         </is>
       </c>
     </row>
@@ -17893,7 +17893,7 @@
       </c>
       <c r="M267" t="inlineStr">
         <is>
-          <t>Những tấm băng-rôn này nằm rải rác khắp Khu Phố Cũ, chờ cậu khám phá! Bíp!</t>
+          <t>Những lá cờ này rải rác khắp Khu Phố Cũ, chờ cậu khám phá đấy! Beep!</t>
         </is>
       </c>
     </row>
@@ -17958,7 +17958,7 @@
       </c>
       <c r="M268" t="inlineStr">
         <is>
-          <t>Với những biểu ngữ nhỏ này, bạn có thể kích hoạt trực tiếp.</t>
+          <t>Những biểu ngữ nhỏ này, cậu có thể kích hoạt trực tiếp luôn.</t>
         </is>
       </c>
     </row>
@@ -18023,7 +18023,7 @@
       </c>
       <c r="M269" t="inlineStr">
         <is>
-          <t>Bíp... Wow, thật ấn tượng! Chiến thắng thuộc về bạn!</t>
+          <t>Bíp... Ồ, thật ấn tượng! Chiến thắng thuộc về cậu rồi!</t>
         </is>
       </c>
     </row>
@@ -18088,7 +18088,7 @@
       </c>
       <c r="M270" t="inlineStr">
         <is>
-          <t>Tít... Quả thật ngươi là Chiến Binh vĩ đại nhất! Chiến thắng thuộc về ngươi!</t>
+          <t>Bíp... Quả thật cậu là Chiến Binh vĩ đại nhất! Chiến thắng thuộc về cậu!</t>
         </is>
       </c>
     </row>
@@ -18153,7 +18153,7 @@
       </c>
       <c r="M271" t="inlineStr">
         <is>
-          <t>{PlayerName}. Can you hear me?</t>
+          <t>{PlayerName}. Cậu nghe thấy tao không?</t>
         </is>
       </c>
     </row>
@@ -18218,7 +18218,7 @@
       </c>
       <c r="M272" t="inlineStr">
         <is>
-          <t>Chỉ là cuộc dạo chơi thôi mà.</t>
+          <t>Chỉ là một buổi đi dạo thôi mà.</t>
         </is>
       </c>
     </row>
@@ -18348,7 +18348,7 @@
       </c>
       <c r="M274" t="inlineStr">
         <is>
-          <t>Cách đi của cậu quả thực khiến chúng tôi bất ngờ. Thực tế, chúng tôi đã phát hiện ra điều đặc biệt từ Mẫu Giấc Mơ Septimont.</t>
+          <t>Cách cậu đi bộ vừa rồi quả là bất ngờ. Thực ra, chúng tôi đã phát hiện ra điều đặc biệt từ Mẫu Giấc Mơ Septimont.</t>
         </is>
       </c>
     </row>
@@ -18413,7 +18413,7 @@
       </c>
       <c r="M275" t="inlineStr">
         <is>
-          <t>Chắc chắn cậu vẫn còn nhớ lời mời tham dự Liên hoan Film Somnoire mà cậu nhận được, phải không?</t>
+          <t>Tôi tin là cậu vẫn còn nhớ lời mời tham dự Liên hoan phim Somnoire chứ, phải không?</t>
         </is>
       </c>
     </row>
@@ -18608,7 +18608,7 @@
       </c>
       <c r="M278" t="inlineStr">
         <is>
-          <t>Worry not. Tóm lại, chúng ta đã nắm được đại khái nguyên nhân khiến hoạt động ở sâu trong Somnoire đột ngột tăng mạnh.</t>
+          <t>Đừng lo. Tóm lại, chúng ta đã nắm được nguyên nhân cơ bản đằng sau sự bùng nổ hoạt động đột ngột từ vực sâu Somnoire.</t>
         </is>
       </c>
     </row>
@@ -18673,7 +18673,7 @@
       </c>
       <c r="M279" t="inlineStr">
         <is>
-          <t>Tuy nhiên, chúng ta vẫn thiếu mẫu đủ để xác minh giả thuyết. Nếu bạn không phiền, chúng tôi muốn bạn tiêu diệt những Nightmare Tacet Discord còn lại.</t>
+          <t>Tuy nhiên, chúng ta vẫn chưa có đủ mẫu vật để xác minh giả thuyết. Nếu cậu không phiền, chúng tôi muốn nhờ cậu tiêu diệt những Tacet Discord Ác Mộng còn lại.</t>
         </is>
       </c>
     </row>
@@ -18738,7 +18738,7 @@
       </c>
       <c r="M280" t="inlineStr">
         <is>
-          <t>Tọa độ của chúng đã được gửi đến Terminal của bạn. Như thường lệ, bạn sẽ được thưởng cho công sức bỏ ra. Cảm ơn sự hỗ trợ của bạn, {PlayerName}.</t>
+          <t>Tọa độ của họ đã được gửi đến Thiết bị đầu cuối của cậu. Như thường lệ, cậu sẽ được thưởng xứng đáng cho công sức bỏ ra. Cảm ơn sự hỗ trợ của cậu, {PlayerName}.</t>
         </is>
       </c>
     </row>
@@ -18803,7 +18803,7 @@
       </c>
       <c r="M281" t="inlineStr">
         <is>
-          <t>Chúng ta đã xác nhận và thu thập đủ Mẫu Cảnh Mộng, {PlayerName}. Làm tốt lắm.</t>
+          <t>Chúng ta đã xác nhận và thu thập đủ Mẫu Giấc Mơ rồi, {PlayerName}. Làm tốt lắm.</t>
         </is>
       </c>
     </row>
@@ -18868,7 +18868,7 @@
       </c>
       <c r="M282" t="inlineStr">
         <is>
-          <t>Cậu tìm thấy gì?</t>
+          <t>Ngươi tìm thấy gì?</t>
         </is>
       </c>
     </row>
@@ -18933,7 +18933,7 @@
       </c>
       <c r="M283" t="inlineStr">
         <is>
-          <t>Tôi sẽ lấy phần thưởng của mình.</t>
+          <t>Ta sẽ nhận phần thưởng của mình.</t>
         </is>
       </c>
     </row>
@@ -18998,7 +18998,7 @@
       </c>
       <c r="M284" t="inlineStr">
         <is>
-          <t>Không muốn nói với {PlayerName} đâu, nhưng mọi chuyện phức tạp hơn ta tưởng. Meow! Thậm chí ta còn tìm thấy rạp chiếu phim lần trước trong những mẫu này.</t>
+          <t>Thật không muốn nói với cậu đâu, {PlayerName}. Mọi chuyện phức tạp hơn chúng ta tưởng nhiều. Meo! Chúng ta còn tìm thấy cả đoạn phim từ lần trước trong mấy mẫu này nữa.</t>
         </is>
       </c>
     </row>
@@ -19063,7 +19063,7 @@
       </c>
       <c r="M285" t="inlineStr">
         <is>
-          <t>Đừng lo, cậu sẽ nhận được thưởng. Chúng tớ hứa mà. Meow! Đoán xem nào, {PlayerName}? Chúng tớ tìm thấy rạp chiếu phim lần trước trong mấy mẫu này đấy.</t>
+          <t>Đừng lo, cậu sẽ nhận được phần thưởng của mình. Chúng tôi hứa mà. Meo! Đoán xem nào, {PlayerName}? Chúng tôi tìm thấy đoạn phim từ lần trước trong mấy mẫu này đấy.</t>
         </is>
       </c>
     </row>
@@ -19128,7 +19128,7 @@
       </c>
       <c r="M286" t="inlineStr">
         <is>
-          <t>Đừng có ngắt lời. Tôi mới là người phụ trách báo cáo!</t>
+          <t>Đừng có ngắt lời. Ta mới là người phụ trách báo cáo!</t>
         </is>
       </c>
     </row>
@@ -19193,7 +19193,7 @@
       </c>
       <c r="M287" t="inlineStr">
         <is>
-          <t>...Meow.</t>
+          <t>...Meo.</t>
         </is>
       </c>
     </row>
@@ -19258,7 +19258,7 @@
       </c>
       <c r="M288" t="inlineStr">
         <is>
-          <t>Một điều chắc chắn là sự đứt đoạn kết nối của Somnoire thuộc Rinascita có liên quan đến chuyện này.</t>
+          <t>Một điều chắc chắn là sự đứt kết nối của Somnoire ở Rinascita có liên quan đến chuyện này.</t>
         </is>
       </c>
     </row>
@@ -19323,7 +19323,7 @@
       </c>
       <c r="M289" t="inlineStr">
         <is>
-          <t>Tuy nhiên, cho đến nay, chúng tôi vẫn chưa xác định được nguồn gốc của tần số này.</t>
+          <t>Thế nhưng cho đến giờ, chúng ta vẫn chưa xác định được nguồn gốc của tần số đó.</t>
         </is>
       </c>
     </row>
@@ -19388,7 +19388,7 @@
       </c>
       <c r="M290" t="inlineStr">
         <is>
-          <t>Giả thuyết của chúng tôi cho rằng Dark Tide có thể là nguyên nhân đằng sau điều này! Các mẫu Nightmare chúng tôi thu thập đều có dấu vết của Dark Tide!</t>
+          <t>Giả thuyết của chúng tôi là Dark Tide có thể là nguyên nhân! Mẫu Nightmare chúng tôi thu thập được phủ đầy dấu vết của Dark Tide!</t>
         </is>
       </c>
     </row>
@@ -19453,7 +19453,7 @@
       </c>
       <c r="M291" t="inlineStr">
         <is>
-          <t>Tôi phải nói bao nhiêu lần nữa là tôi mới là người làm báo cáo! Hãy giữ những tưởng tượng vô lý đó cho riêng mình!</t>
+          <t>Tao phải nói bao nhiêu lần nữa mới được? Tao mới là người làm báo cáo! Giữ những ý nghĩ vớ vẩn đó cho riêng mày đi!</t>
         </is>
       </c>
     </row>
@@ -19518,7 +19518,7 @@
       </c>
       <c r="M292" t="inlineStr">
         <is>
-          <t>Hãy chú ý đến bất kỳ Nightmare Tacet Discord nào bạn có thể gặp trong chuyến du hành đến các vùng khác của Rinascita, {PlayerName}.</t>
+          <t>Nhớ để mắt đến bất kỳ Tacet Discord Ác Mộng nào trên đường đi đến các khu vực khác của Rinascita nhé, {PlayerName}.</t>
         </is>
       </c>
     </row>
@@ -19583,7 +19583,7 @@
       </c>
       <c r="M293" t="inlineStr">
         <is>
-          <t>Khoan... Làm sao để mở nó nhỉ...</t>
+          <t>Khoan... Làm sao để mở cái này nhỉ...</t>
         </is>
       </c>
     </row>
@@ -19648,7 +19648,7 @@
       </c>
       <c r="M294" t="inlineStr">
         <is>
-          <t>Chuyện gì đang xảy ra vậy?</t>
+          <t>Có chuyện gì vậy?</t>
         </is>
       </c>
     </row>
@@ -19713,7 +19713,7 @@
       </c>
       <c r="M295" t="inlineStr">
         <is>
-          <t>Tôi đang thu thập Sacred Muối cho nhu cầu tương lai.</t>
+          <t>Tớ đang thu thập Muối Thần để dùng sau này.</t>
         </is>
       </c>
     </row>
@@ -19778,7 +19778,7 @@
       </c>
       <c r="M296" t="inlineStr">
         <is>
-          <t>Công việc của một Quản Sự không được phép có sai sót. Tôi phải hết sức chăm lo cho phúc lợi của các Tu Sĩ.</t>
+          <t>Công việc của một Quản Sự không cho phép sai sót. Ta phải hết sức chăm lo cho phúc lợi của các Tín Đồ.</t>
         </is>
       </c>
     </row>
@@ -19843,7 +19843,7 @@
       </c>
       <c r="M297" t="inlineStr">
         <is>
-          <t>Những người tử vì đạo đã hy sinh tất cả vì sứ mệnh cứu Ragunna. Dù thất bại, họ vẫn xứng đáng được sống những ngày tháng bình yên...</t>
+          <t>Những người tử đạo đã hy sinh tất cả vì sứ mệnh cứu Ragunna. Dù thất bại, họ vẫn xứng đáng được sống những ngày tháng bình yên...</t>
         </is>
       </c>
     </row>
@@ -19908,7 +19908,7 @@
       </c>
       <c r="M298" t="inlineStr">
         <is>
-          <t>Muối Thánh là dành cho bọn họ à?</t>
+          <t>Muối Thánh là để cho bọn chúng à?</t>
         </is>
       </c>
     </row>
@@ -19973,7 +19973,7 @@
       </c>
       <c r="M299" t="inlineStr">
         <is>
-          <t>Vì vậy, tôi sẽ thực hiện nghi lễ thanh tẩy và thánh hóa bằng Muối Thánh trước mặt họ với tất cả đồ dự trữ.</t>
+          <t>Đó là lý do ta sẽ thực hiện nghi lễ thanh tẩy và thánh hóa bằng Muối Thánh trước mặt họ với tất cả các vật phẩm.</t>
         </is>
       </c>
     </row>
@@ -20038,7 +20038,7 @@
       </c>
       <c r="M300" t="inlineStr">
         <is>
-          <t>Để khiến chúng tin rằng mình đang nhận bữa ăn nuôi dưỡng từ Thần Tính, uống máu thánh ban sự khai sáng. Vậy thì chúng không có lý do gì để từ chối.</t>
+          <t>Dẫn dắt chúng tin rằng mình đang hưởng bữa ăn nuôi dưỡng của Thần Tính, uống máu thánh ban cho sự khai sáng. Như vậy, chúng sẽ chẳng có lý do gì để từ chối.</t>
         </is>
       </c>
     </row>
@@ -20103,7 +20103,7 @@
       </c>
       <c r="M301" t="inlineStr">
         <is>
-          <t>Nhưng gần đây, chúng ta đang thiếu Muối Thánh. Là một Acolyte của Bộ Nghi Lễ Thần Thánh, tôi...</t>
+          <t>Nhưng dạo này, chúng ta đang thiếu Muối Thánh. Là một Tín Đồ của Bộ Nghi Lễ Thánh, tôi...</t>
         </is>
       </c>
     </row>
@@ -20168,7 +20168,7 @@
       </c>
       <c r="M302" t="inlineStr">
         <is>
-          <t>(Anh ấy cũng có vẻ bất an... Tốt nhất là đừng thúc ép. Ta nên tìm cách giúp đỡ thôi.)</t>
+          <t>(Cậu ấy cũng có vẻ bất an... Tốt nhất là đừng thúc ép. Ta nên tìm cách giúp đỡ.)</t>
         </is>
       </c>
     </row>
@@ -20233,7 +20233,7 @@
       </c>
       <c r="M303" t="inlineStr">
         <is>
-          <t>Liệu Hội Đoàn đã lường trước tình huống này?</t>
+          <t>Hội Đoàn đã lường trước tình huống này chưa?</t>
         </is>
       </c>
     </row>
@@ -20298,7 +20298,7 @@
       </c>
       <c r="M304" t="inlineStr">
         <is>
-          <t>À, đúng rồi. Chúng tôi đã để dành một ít Muối Thánh trong Xưởng Dệt cho những lúc như thế này. Nó được cất giữ trong Rương Tam Tượng và những nơi khác...</t>
+          <t>À, đúng rồi. Ta đã để dành một ít Muối Thánh trong Xưởng Dệt cho những lúc như thế này. Chúng được cất trong Rương Triptych và một số nơi khác...</t>
         </is>
       </c>
     </row>
@@ -20363,7 +20363,7 @@
       </c>
       <c r="M305" t="inlineStr">
         <is>
-          <t>Nếu gặp được thứ gì, hãy mang đến cho tôi. Tôi sẽ trả công hậu hĩnh. Bạn thấy thế nào?</t>
+          <t>Nếu tìm thấy cái nào, mang đến đây cho ta. Ta sẽ hậu tạ xứng đáng. Ngươi thấy thế nào?</t>
         </is>
       </c>
     </row>
@@ -20428,7 +20428,7 @@
       </c>
       <c r="M306" t="inlineStr">
         <is>
-          <t>Thỏa thuận thế là xong.</t>
+          <t>Thỏa thuận rồi đấy.</t>
         </is>
       </c>
     </row>
@@ -20493,7 +20493,7 @@
       </c>
       <c r="M307" t="inlineStr">
         <is>
-          <t>Cảm ơn sự giúp đỡ và cống hiến của bạn. Hãy xem thử có gì hợp ý không nhé.</t>
+          <t>Cảm ơn vì sự giúp đỡ và tận tâm của cậu. Hãy xem thử có gì hợp mắt không nhé.</t>
         </is>
       </c>
     </row>
@@ -20558,7 +20558,7 @@
       </c>
       <c r="M308" t="inlineStr">
         <is>
-          <t>Nguyện Sentinel luôn phù hộ cho bạn.</t>
+          <t>Nguyện Sentinel luôn phù hộ cho ngươi.</t>
         </is>
       </c>
     </row>
@@ -20623,7 +20623,7 @@
       </c>
       <c r="M309" t="inlineStr">
         <is>
-          <t>Như thế này à? Không, không phải... Sao lại...</t>
+          <t>Như thế này à? Không, không phải... Sao nhỉ...</t>
         </is>
       </c>
     </row>
@@ -20688,7 +20688,7 @@
       </c>
       <c r="M310" t="inlineStr">
         <is>
-          <t>{PlayerName}, tôi vừa cảm nhận được một Nút Mộng Cảnh được khôi phục ở Sanguis Plateaus. Và không ngạc nhiên, đó là do cậu làm.</t>
+          <t>{PlayerName}, ta vừa cảm nhận được một Nút Giấc Mơ ở Cao Nguyên Sanguis được khôi phục. Và không ngạc nhiên, chính là do cậu làm đấy.</t>
         </is>
       </c>
     </row>
@@ -20753,7 +20753,7 @@
       </c>
       <c r="M311" t="inlineStr">
         <is>
-          <t>Bạn thuật lại những gì đã xảy ra với Gatekeeper Huyền Ngân.</t>
+          <t>Cậu kể lại những gì đã xảy ra với Ebony Gatekeeper.</t>
         </is>
       </c>
     </row>
@@ -20818,7 +20818,7 @@
       </c>
       <c r="M312" t="inlineStr">
         <is>
-          <t>Một thanh kiếm đen cháy trong lửa, khi chạm vào sẽ xuất hiện những Nightmares mang tần số Dark Tide? Phải chăng là...</t>
+          <t>Một thanh kiếm đen cháy rực ngọn lửa, khi chạm vào lại tuôn ra những Ác Mộng mang tần số Dark Tide? Lẽ nào...</t>
         </is>
       </c>
     </row>
@@ -20883,7 +20883,7 @@
       </c>
       <c r="M313" t="inlineStr">
         <is>
-          <t>Nó đang kìm hãm các Nightmare Tacet Discord.</t>
+          <t>Nó đang kìm hãm bọn Tacet Discord Ác Mộng.</t>
         </is>
       </c>
     </row>
@@ -20948,7 +20948,7 @@
       </c>
       <c r="M314" t="inlineStr">
         <is>
-          <t>Nó đang canh giữ Nút Giấc Mộng phải không?</t>
+          <t>Nó có đang canh giữ Nút Giấc Mơ không?</t>
         </is>
       </c>
     </row>
@@ -21013,7 +21013,7 @@
       </c>
       <c r="M315" t="inlineStr">
         <is>
-          <t>Đúng vậy... Có vẻ như là như vậy. Câu hỏi là, ai đã đặt thanh kiếm ở đó?</t>
+          <t>Đúng vậy... Có vẻ là như thế. Câu hỏi là, ai đã đặt thanh kiếm ở đó?</t>
         </is>
       </c>
     </row>
@@ -21078,7 +21078,7 @@
       </c>
       <c r="M316" t="inlineStr">
         <is>
-          <t>Tôi không thể chắc chắn. Có lẽ nó được đặt ở đó chỉ để kìm hãm Tacet Discord. Nhưng... bởi ai?</t>
+          <t>Ta không thể khẳng định chắc chắn. Có lẽ nó được đặt ở đó chỉ để kìm hãm các Tacet Discord. Nhưng... bởi ai?</t>
         </is>
       </c>
     </row>
@@ -21143,7 +21143,7 @@
       </c>
       <c r="M317" t="inlineStr">
         <is>
-          <t>Phải chăng đó là một Resonator đặc biệt có thể cảm nhận Dreamscapes, hay sức mạnh này bắt nguồn từ chính Somnoire?</t>
+          <t>Đó là một Resonator đặc biệt có thể nhìn thấy Dreamscapes, hay năng lực này đến từ chính Somnoire?</t>
         </is>
       </c>
     </row>
@@ -21208,7 +21208,7 @@
       </c>
       <c r="M318" t="inlineStr">
         <is>
-          <t>Khi thanh kiếm ấy biến mất, tôi cảm nhận được một tần số ấm áp trong gió.</t>
+          <t>Khi thanh kiếm ấy biến mất, ta cảm nhận được một tần số ấm áp trong gió.</t>
         </is>
       </c>
     </row>
@@ -21273,7 +21273,7 @@
       </c>
       <c r="M319" t="inlineStr">
         <is>
-          <t>Thật phi thường... Nếu không phiền, bạn có thể khôi phục các nút còn lại không, {PlayerName}? Tôi sẽ đánh dấu vị trí cho bạn.</t>
+          <t>Thật phi thường... Nếu không phiền, ngươi có thể khôi phục những điểm nút còn lại không, {PlayerName}? Ta sẽ đánh dấu vị trí cho ngươi.</t>
         </is>
       </c>
     </row>
@@ -21338,7 +21338,7 @@
       </c>
       <c r="M320" t="inlineStr">
         <is>
-          <t>Nếu phỏng đoán của tôi đúng, câu trả lời về nguồn gốc thanh kiếm đang ẩn giấu trong các nút còn lại.</t>
+          <t>Nếu ta không lầm, câu trả lời về nguồn gốc thanh kiếm đang ẩn giấu trong những nút cờ còn lại.</t>
         </is>
       </c>
     </row>
@@ -21403,7 +21403,7 @@
       </c>
       <c r="M321" t="inlineStr">
         <is>
-          <t>{PlayerName}... Nhiều năm trước, tôi đã học được một câu thơ... trong giấc mơ, từ một người ở Huanglong.</t>
+          <t>Nhiều năm trước, ta từng học một câu thơ... trong giấc mơ, từ một người ở Huanglong.</t>
         </is>
       </c>
     </row>
@@ -21468,7 +21468,7 @@
       </c>
       <c r="M322" t="inlineStr">
         <is>
-          <t>"Hình hài họ đã tàn, song linh hồn bất diệt. Anh dũng hy sinh, họ mãi là anh hùng."</t>
+          <t>Nó đọc... "Thân xác họ đã ngã, nhưng linh hồn vẫn bất diệt. Anh dũng trong cái chết, họ được tôn vinh như những người hùng."</t>
         </is>
       </c>
     </row>
@@ -21533,7 +21533,7 @@
       </c>
       <c r="M323" t="inlineStr">
         <is>
-          <t>Có vẻ như cậu đã hiểu ra mấy thanh kiếm đó rồi nhỉ?</t>
+          <t>Nghe có vẻ cậu đã hiểu ra mấy thanh kiếm đó rồi nhỉ?</t>
         </is>
       </c>
     </row>
@@ -21598,7 +21598,7 @@
       </c>
       <c r="M324" t="inlineStr">
         <is>
-          <t>Yes. Và có vẻ như tôi đã phạm phải sai lầm trong đánh giá.</t>
+          <t>Đúng vậy. Và có vẻ như ta đã phạm phải một sai lầm trong phán đoán.</t>
         </is>
       </c>
     </row>
@@ -21728,7 +21728,7 @@
       </c>
       <c r="M326" t="inlineStr">
         <is>
-          <t>Và đó là lý do tại sao những tần số cấu thành những thanh kiếm ấy cuối cùng đã phai nhạt, vươn tới Septimont...</t>
+          <t>Và đó chính là lý do những tần số cấu thành nên thanh kiếm ấy dần tan biến, vươn về phía Septimont...</t>
         </is>
       </c>
     </row>
@@ -21793,7 +21793,7 @@
       </c>
       <c r="M327" t="inlineStr">
         <is>
-          <t>Họ mong muốn được trở về nhà. Những chiến binh Septimont thà trở về quê hương còn hơn tìm sự bình yên vĩnh cửu trong Dreamscapes.</t>
+          <t>Họ chỉ mong được trở về nhà. Những chiến binh Septimont thà trở về quê hương còn hơn tìm sự bình yên vĩnh cửu trong Dreamscapes.</t>
         </is>
       </c>
     </row>
@@ -21923,7 +21923,7 @@
       </c>
       <c r="M329" t="inlineStr">
         <is>
-          <t>À, phải rồi. Ta vừa phát hiện điều thú vị trong Node cuối cùng của Sanguis Plateaus.</t>
+          <t>À, đúng rồi. Ta vừa phát hiện điều thú vị ở Nút cuối cùng của Cao nguyên Sanguis.</t>
         </is>
       </c>
     </row>
@@ -21988,7 +21988,7 @@
       </c>
       <c r="M330" t="inlineStr">
         <is>
-          <t>Là anh hùng mà họ mong đợi từ lâu, bạn nên nhận lấy nó.</t>
+          <t>Là anh hùng mà họ hằng mong đợi, ngươi nên nhận lấy nó.</t>
         </is>
       </c>
     </row>
@@ -22053,7 +22053,7 @@
       </c>
       <c r="M331" t="inlineStr">
         <is>
-          <t>Lũ TD lại đang lảng vảng khắp nơi...</t>
+          <t>Mấy con TD này lại lăng xăng khắp nơi rồi...</t>
         </is>
       </c>
     </row>
@@ -22118,7 +22118,7 @@
       </c>
       <c r="M332" t="inlineStr">
         <is>
-          <t>Tôi cần sự giúp đỡ với việc này.</t>
+          <t>Tôi cần một chút trợ giúp ở đây.</t>
         </is>
       </c>
     </row>
@@ -22183,7 +22183,7 @@
       </c>
       <c r="M333" t="inlineStr">
         <is>
-          <t>Mong tiếng vỗ tay sẽ chào đón bạn!</t>
+          <t>Hãy dành tiếng vỗ tay chào đón ngươi!</t>
         </is>
       </c>
     </row>
@@ -22248,7 +22248,7 @@
       </c>
       <c r="M334" t="inlineStr">
         <is>
-          <t>À, chiến binh... Tôi có quen cậu ở đâu không nhỉ? Cậu có tham gia Đại Agon không?</t>
+          <t>À, chiến binh... Ta có quen cậu ở đâu không nhỉ? Cậu có tham gia Đại Agon không?</t>
         </is>
       </c>
     </row>
@@ -22378,7 +22378,7 @@
       </c>
       <c r="M336" t="inlineStr">
         <is>
-          <t>Bạn đang nhìn vào nhà vô địch năm nay đấy.</t>
+          <t>Cậu đang nhìn nhà vô địch năm nay đấy.</t>
         </is>
       </c>
     </row>
@@ -22443,7 +22443,7 @@
       </c>
       <c r="M337" t="inlineStr">
         <is>
-          <t>Vậy à? Đợi chút, chắc hẳn cậu... Đúng rồi, cậu chính là quán quân Agon năm nay!</t>
+          <t>Vậy à? Khoan đã, chắc hẳn cậu... Đúng rồi, cậu chính là quán quân Agon năm nay!</t>
         </is>
       </c>
     </row>
@@ -22508,7 +22508,7 @@
       </c>
       <c r="M338" t="inlineStr">
         <is>
-          <t>À, hóa ra là cậu! Tưởng quen quen.</t>
+          <t>A, hóa ra là cậu! Tao cứ thấy quen quen.</t>
         </is>
       </c>
     </row>
@@ -22573,7 +22573,7 @@
       </c>
       <c r="M339" t="inlineStr">
         <is>
-          <t>Ta đã ở khu săn bắn này lâu đến mức không nhớ nổi, nên xin thứ lỗi vì ban đầu không nhận ra nhà vô địch yêu quý của chúng ta.</t>
+          <t>Tớ đã ở khu săn bắn này lâu đến mức không nhớ nổi, nên xin thứ lỗi nếu không nhận ra nhà vô địch yêu quý của chúng ta ngay từ cái nhìn đầu tiên.</t>
         </is>
       </c>
     </row>
@@ -22638,7 +22638,7 @@
       </c>
       <c r="M340" t="inlineStr">
         <is>
-          <t>Dù sao, tôi vẫn rất biết ơn vì người xuất hiện lại là bạn.</t>
+          <t>Dù sao thì ta cũng rất biết ơn vì người xuất hiện lại là cậu.</t>
         </is>
       </c>
     </row>
@@ -22703,7 +22703,7 @@
       </c>
       <c r="M341" t="inlineStr">
         <is>
-          <t>Sao lại thế?</t>
+          <t>Sao cơ?</t>
         </is>
       </c>
     </row>
@@ -22768,7 +22768,7 @@
       </c>
       <c r="M342" t="inlineStr">
         <is>
-          <t>Vấn đề là, chúng ta gặp chút rắc rối rồi.</t>
+          <t>Vấn đề là, chúng ta gặp chút trục trặc rồi.</t>
         </is>
       </c>
     </row>
@@ -22833,7 +22833,7 @@
       </c>
       <c r="M343" t="inlineStr">
         <is>
-          <t>Thủy Triều High đã kéo đến vô số TD, và ngay cả khi nó rút đi, lũ khốn đó vẫn không chịu rời đi.</t>
+          <t>Thủy Triều Cao kéo theo vô số Tổ Tacet, và ngay cả khi nước rút, lũ khốn đó vẫn ngoan cố không chịu rời đi.</t>
         </is>
       </c>
     </row>
@@ -22898,7 +22898,7 @@
       </c>
       <c r="M344" t="inlineStr">
         <is>
-          <t>Không thể để chúng chạy lung tung khắp nơi được.</t>
+          <t>Không thể để chúng chạy lung tung ngoài này được.</t>
         </is>
       </c>
     </row>
@@ -23028,7 +23028,7 @@
       </c>
       <c r="M346" t="inlineStr">
         <is>
-          <t>Chúng không được tính là mục tiêu săn bắt à?</t>
+          <t>Chúng không được tính là mục tiêu săn bắn à?</t>
         </is>
       </c>
     </row>
@@ -23093,7 +23093,7 @@
       </c>
       <c r="M347" t="inlineStr">
         <is>
-          <t>Đúng vậy. Một chiến binh thực thụ luôn phải mài giũa lưỡi kiếm, ngay cả sau khi săn mồi.</t>
+          <t>Đúng thế. Một chiến binh thực thụ phải luôn mài sắc lưỡi kiếm của mình, ngay cả sau khi săn mồi.</t>
         </is>
       </c>
     </row>
@@ -23158,7 +23158,7 @@
       </c>
       <c r="M348" t="inlineStr">
         <is>
-          <t>Cuộc săn trong vòng này đã kết thúc, và những TD này chỉ là những mẩu vụn rải rác thậm chí không đủ để lên danh sách. Tuy nhiên, chúng vẫn là mối đe dọa.</t>
+          <t>Cuộc săn lần này đã kết thúc, và mấy con Tacet Discord này chỉ như những mẩu vụn vương vãi, thậm chí không đáng để ghi vào danh sách. Nhưng chúng vẫn là mối nguy hiểm.</t>
         </is>
       </c>
     </row>
@@ -23223,7 +23223,7 @@
       </c>
       <c r="M349" t="inlineStr">
         <is>
-          <t>Địa hình xung quanh khá phức tạp, bạn cần chú ý quan sát trước khi hành động thực sự bắt đầu.</t>
+          <t>Địa hình xung quanh khá phức tạp, cậu nên để mắt cẩn thận trước khi hành động thực sự bắt đầu.</t>
         </is>
       </c>
     </row>
@@ -23288,7 +23288,7 @@
       </c>
       <c r="M350" t="inlineStr">
         <is>
-          <t>Một thợ săn TD phải có đôi mắt sắc như đại bàng và sức bùng nổ của sư tử.</t>
+          <t>Thợ săn Tacet Discord phải có đôi mắt tinh tường như đại bàng và sức mạnh bùng nổ như sư tử.</t>
         </is>
       </c>
     </row>
@@ -23353,7 +23353,7 @@
       </c>
       <c r="M351" t="inlineStr">
         <is>
-          <t>Chúng ta chỉ đang lần theo dấu vết thôi à?</t>
+          <t>Chúng ta chỉ đi theo dõi chúng thôi à?</t>
         </is>
       </c>
     </row>
@@ -23418,7 +23418,7 @@
       </c>
       <c r="M352" t="inlineStr">
         <is>
-          <t>Theo dõi Mục tiêu là công việc đòi hỏi kỹ năng. Chỉ cần một sơ suất nhỏ, con mồi sẽ vuột khỏi tầm tay bạn.</t>
+          <t>Theo dõi Tacet Discord là công việc đòi hỏi kỹ năng cao. Chỉ cần một chút sơ suất, con mồi sẽ vuột khỏi tầm tay ngay.</t>
         </is>
       </c>
     </row>
@@ -23483,7 +23483,7 @@
       </c>
       <c r="M353" t="inlineStr">
         <is>
-          <t>Tuy nhiên, tôi để ý bạn đã thăm dò các dấu vết gần đây kể từ khi đến. Có lẽ bạn đã có kinh nghiệm trong việc này?</t>
+          <t>Nhưng từ lúc đến, mình thấy cậu cứ dò xét dấu vết quanh đây. Chắc cậu cũng có kinh nghiệm trong chuyện này?</t>
         </is>
       </c>
     </row>
@@ -23548,7 +23548,7 @@
       </c>
       <c r="M354" t="inlineStr">
         <is>
-          <t>Tôi có thể biết đôi điều về săn bắn đấy.</t>
+          <t>Ta có lẽ biết đôi điều về săn bắn.</t>
         </is>
       </c>
     </row>
@@ -23613,7 +23613,7 @@
       </c>
       <c r="M355" t="inlineStr">
         <is>
-          <t>Mình đã nhận được sự chấp thuận từ Hội Thợ Săn rồi.</t>
+          <t>Tớ đã được Hội Thợ Săn chấp thuận rồi.</t>
         </is>
       </c>
     </row>
@@ -23678,7 +23678,7 @@
       </c>
       <c r="M356" t="inlineStr">
         <is>
-          <t>Haha. Bản năng thợ săn của tôi vẫn sắc bén như xưa.</t>
+          <t>Haha. Bản năng thợ săn của tao vẫn còn bén như xưa.</t>
         </is>
       </c>
     </row>
@@ -23743,7 +23743,7 @@
       </c>
       <c r="M357" t="inlineStr">
         <is>
-          <t>Giấy chấp thuận từ Hội Thợ Săn à? Có phải họ đang làm cái mới bây giờ không? Trời ơi, tôi ở đây lâu quá rồi.</t>
+          <t>Giấy phép từ Hội Thợ Săn à? Có phải họ mới áp dụng quy định này không? Trời, tôi ở đây lâu quá rồi thật.</t>
         </is>
       </c>
     </row>
@@ -23808,7 +23808,7 @@
       </c>
       <c r="M358" t="inlineStr">
         <is>
-          <t>Thế thì không dài dòng nữa, cuộc săn bắt bắt đầu thôi!</t>
+          <t>Vậy thì, không dài dòng nữa, cuộc săn bắt bắt đầu thôi!</t>
         </is>
       </c>
     </row>
@@ -23873,7 +23873,7 @@
       </c>
       <c r="M359" t="inlineStr">
         <is>
-          <t>Nguyện vinh quang cùng ta, bạn ơi!</t>
+          <t>Chúc vinh quang luôn ở bên chúng ta, bạn tôi!</t>
         </is>
       </c>
     </row>
@@ -23938,7 +23938,7 @@
       </c>
       <c r="M360" t="inlineStr">
         <is>
-          <t>Ha! Ngay cả con TD khét tiếng nhất cũng bị cậu giải quyết rồi!</t>
+          <t>Ha! Cả cái Tacet Discord khét tiếng nhất cũng bị cậu hạ gục rồi!</t>
         </is>
       </c>
     </row>
@@ -24003,7 +24003,7 @@
       </c>
       <c r="M361" t="inlineStr">
         <is>
-          <t>Và thế là chúng ta có thể tận hưởng chút bình yên thoáng qua tại Sanguis Plateaus.</t>
+          <t>Và thế là, chúng ta có thể tận hưởng chút bình yên ngắn ngủi tại Cao nguyên Sanguis.</t>
         </is>
       </c>
     </row>
@@ -24068,7 +24068,7 @@
       </c>
       <c r="M362" t="inlineStr">
         <is>
-          <t>Có vẻ như tớ không phải lo về TDs trong một thời gian rồi. Chắc tớ nên đi làm gì đó khác thôi.</t>
+          <t>Có vẻ là ta không phải lo về mấy Tổ Tacet trong một thời gian rồi. Chắc ta nên làm gì đó khác thôi.</t>
         </is>
       </c>
     </row>
@@ -24133,7 +24133,7 @@
       </c>
       <c r="M363" t="inlineStr">
         <is>
-          <t>Cái gì khác, ý cậu là?</t>
+          <t>Ý cậu là gì khác?</t>
         </is>
       </c>
     </row>
@@ -24198,7 +24198,7 @@
       </c>
       <c r="M364" t="inlineStr">
         <is>
-          <t>Thật không thể tin được khi một nhà vô địch trẻ như cậu lại xuất hiện trong những năm tôi ở khu săn bắn này. Đây hẳn là sự sắp đặt của số phận.</t>
+          <t>Thật không thể tin được khi một nhà vô địch trẻ như cậu lại xuất hiện trong những năm ta làm việc tại khu săn bắn. Đây hẳn là sự sắp đặt của vận mệnh.</t>
         </is>
       </c>
     </row>
@@ -24263,7 +24263,7 @@
       </c>
       <c r="M365" t="inlineStr">
         <is>
-          <t>Tôi định ra ngoài một thời gian. Đi xem thế giới. Quay lại khi đợt Triều High kế tiếp đến, và sẽ có một trận đấu tay đôi với mấy con TD.</t>
+          <t>Ta định ra ngoài một thời gian. Đi xem thế giới. Quay lại khi đợt Đại Thủy triều kế tiếp đến, rồi đích thân xông pha với lũ TD đó.</t>
         </is>
       </c>
     </row>
@@ -24328,7 +24328,7 @@
       </c>
       <c r="M366" t="inlineStr">
         <is>
-          <t>Hẹn gặp lại, chiến binh đồng hành!</t>
+          <t>Hẹn gặp lại, đồng đội!</t>
         </is>
       </c>
     </row>
@@ -24393,7 +24393,7 @@
       </c>
       <c r="M367" t="inlineStr">
         <is>
-          <t>Test miễn phí! Test miễn phí! Đến đây nhận test miễn phí ngay nào!</t>
+          <t>Kiểm tra miễn phí! Kiểm tra miễn phí! Đến đây kiểm tra miễn phí ngay nào!</t>
         </is>
       </c>
     </row>
@@ -24458,7 +24458,7 @@
       </c>
       <c r="M368" t="inlineStr">
         <is>
-          <t>Test miễn phí! Test miễn phí! Đến đây nhận test miễn phí ngay nào!</t>
+          <t>Kiểm tra miễn phí! Kiểm tra miễn phí! Đến đây kiểm tra miễn phí ngay nào!</t>
         </is>
       </c>
     </row>
@@ -24523,7 +24523,7 @@
       </c>
       <c r="M369" t="inlineStr">
         <is>
-          <t>Tại sao tôi lại muốn một bài test miễn phí chứ?</t>
+          <t>Tại sao tôi lại muốn một bài kiểm tra miễn phí chứ?</t>
         </is>
       </c>
     </row>
@@ -24588,7 +24588,7 @@
       </c>
       <c r="M370" t="inlineStr">
         <is>
-          <t>Thật lòng mà nói, phải khen tinh thần hăng hái với bài kiểm tra của cậu. Tớ thấy nhóm các cậu là nhóm nhiệt huyết nhất từ trước đến giờ!</t>
+          <t>Thật lòng mà nói. Phải khen tinh thần học thi của cậu đấy. Tao phải công nhận, lứa các cậu là lứa nhiệt huyết nhất tao từng thấy!</t>
         </is>
       </c>
     </row>
@@ -24718,7 +24718,7 @@
       </c>
       <c r="M372" t="inlineStr">
         <is>
-          <t>Đó không phải là ý tôi khi hỏi câu đó.</t>
+          <t>Câu hỏi đó không phải ý tao muốn hỏi.</t>
         </is>
       </c>
     </row>
@@ -24783,7 +24783,7 @@
       </c>
       <c r="M373" t="inlineStr">
         <is>
-          <t>À, nó cũng có thể hiểu theo nhiều cách. Dù sao thì bài test cũng đã bắt đầu trong lúc chúng ta nói chuyện rồi—</t>
+          <t>Chà, nó cũng có thể hiểu theo nhiều cách. Dù sao thì bài kiểm tra cũng đã bắt đầu trong lúc chúng ta nói chuyện rồi—</t>
         </is>
       </c>
     </row>
@@ -24848,7 +24848,7 @@
       </c>
       <c r="M374" t="inlineStr">
         <is>
-          <t>Đây là bài test trình độ chiến đấu. Hãy thể hiện những cú đá tốt nhất và hướng tới chứng chỉ đẳng cấp cao nhất!</t>
+          <t>Đây là bài kiểm tra trình độ chiến đấu. Hãy thể hiện những cú đá đẹp nhất và hướng tới chứng nhận đẳng cấp cao nhất!</t>
         </is>
       </c>
     </row>
@@ -24913,7 +24913,7 @@
       </c>
       <c r="M375" t="inlineStr">
         <is>
-          <t>Sự sụp đổ của Exostrider không hề lặng lẽ. Ánh sáng của Reactor Drive xuyên qua bóng tối, và những tần số ấm áp vẫn còn vang vọng đến tận ngày nay.</t>
+          <t>Sự sụp đổ của Exostrider chẳng hề lặng lẽ. Ánh sáng từ Bộ Truyền Động Phản Ứng xuyên thủng bóng tối, và dư âm tần số ấm áp vẫn còn vang vọng đến tận ngày nay.</t>
         </is>
       </c>
     </row>
@@ -24978,7 +24978,7 @@
       </c>
       <c r="M376" t="inlineStr">
         <is>
-          <t>Terminal của bạn đã bắt được một ánh sáng ấm áp—điều này không phải ngẫu nhiên. Rốt cuộc, những tần số tương đồng thường bị hút vào nhau.</t>
+          <t>Thiết bị đầu cuối của cậu đã bắt được một luồng dư quang ấm áp—điều này không phải ngẫu nhiên. Bởi lẽ, những tần số tương đồng thường bị hút về phía nhau.</t>
         </is>
       </c>
     </row>
@@ -25043,7 +25043,7 @@
       </c>
       <c r="M377" t="inlineStr">
         <is>
-          <t>Đồng điệu cùng tần số, tôi là Arsenio. Bạn có sẵn lòng nhận lời mời đến trại của chúng tôi không?</t>
+          <t>Đồng nghiệp mang cùng tần số, tôi là Arsenio. Cô có muốn nhận lời mời đến trại của chúng tôi không?</t>
         </is>
       </c>
     </row>
@@ -25108,7 +25108,7 @@
       </c>
       <c r="M378" t="inlineStr">
         <is>
-          <t>Chắc chắn rồi.</t>
+          <t>Được thôi.</t>
         </is>
       </c>
     </row>
@@ -25173,7 +25173,7 @@
       </c>
       <c r="M379" t="inlineStr">
         <is>
-          <t>Hiện giờ tôi đang bận chút việc.</t>
+          <t>Bây giờ tao đang bận tí.</t>
         </is>
       </c>
     </row>
@@ -25238,7 +25238,7 @@
       </c>
       <c r="M380" t="inlineStr">
         <is>
-          <t>Cảm ơn vì đã nhận lời mời của ta. Ta sẽ gửi tọa độ cho ngươi ngay.</t>
+          <t>Cảm ơn cậu đã nhận lời mời của tớ. Tớ sẽ gửi tọa độ ngay đây.</t>
         </is>
       </c>
     </row>
@@ -25303,7 +25303,7 @@
       </c>
       <c r="M381" t="inlineStr">
         <is>
-          <t>Cảm ơn cậu đã phản hồi. Có lẽ tớ có thể gửi tọa độ trước cho cậu, rồi cậu có thể đến thăm bất cứ lúc nào cậu muốn.</t>
+          <t>Cảm ơn cậu đã hồi đáp. Có lẽ tôi có thể gửi tọa độ trước cho cậu, rồi cậu có thể đến bất cứ lúc nào cậu muốn.</t>
         </is>
       </c>
     </row>
@@ -25368,7 +25368,7 @@
       </c>
       <c r="M382" t="inlineStr">
         <is>
-          <t>Được, tôi sẽ đến ngay.</t>
+          <t>Được rồi, tôi sẽ đến ngay.</t>
         </is>
       </c>
     </row>
@@ -25433,7 +25433,7 @@
       </c>
       <c r="M383" t="inlineStr">
         <is>
-          <t>Hiện tại tôi đang bận chút việc. Tôi sẽ đến khi có thời gian.</t>
+          <t>Bây giờ tao đang bận tí. Tao sẽ qua khi nào rảnh.</t>
         </is>
       </c>
     </row>
@@ -25498,7 +25498,7 @@
       </c>
       <c r="M384" t="inlineStr">
         <is>
-          <t>Cảm ơn bạn đã đến. Tôi là mech Solsworn, Arsenio.</t>
+          <t>Cảm ơn vì đã đến. Ta là cỗ máy Solsworn, Arsenio.</t>
         </is>
       </c>
     </row>
@@ -25563,7 +25563,7 @@
       </c>
       <c r="M385" t="inlineStr">
         <is>
-          <t>Nơi có ánh sáng, bóng tối luôn rình rập. Hiện tượng được gọi là Void Storm đang xóa bỏ tần số tồn tại của chúng ta ngay lúc này...</t>
+          <t>Nơi có ánh sáng, bóng tối luôn rình rập. Hiện tượng Bão Hư Không đang xóa sổ tần số tồn tại của chúng ta ngay lúc này...</t>
         </is>
       </c>
     </row>
@@ -25628,7 +25628,7 @@
       </c>
       <c r="M386" t="inlineStr">
         <is>
-          <t>Nó nuốt chửng mọi thứ trên đường đi, chỉ để lại những Terminal bị tha hóa. Những Terminal này được gọi là Những Băng Cuối Cùng.</t>
+          <t>Nó nuốt chửng mọi thứ trên đường đi, chỉ để lại những Thiết bị đầu cuối bị hư hỏng. Những thiết bị đó được gọi là Những Băng Cuối Cùng.</t>
         </is>
       </c>
     </row>
@@ -25693,7 +25693,7 @@
       </c>
       <c r="M387" t="inlineStr">
         <is>
-          <t>Bên trong, chúng ghi lại tinh hoa của những người đã khuất, và có thể lại tỏa sáng một khi được thanh tẩy khỏi ảnh hưởng của Void Storm.</t>
+          <t>Bên trong, họ ghi lại tinh hoa của những người đã khuất, và có thể một lần nữa nhìn thấy ánh sáng ban ngày khi đã được thanh tẩy khỏi ảnh hưởng của Bão Hư Không.</t>
         </is>
       </c>
     </row>
@@ -25758,7 +25758,7 @@
       </c>
       <c r="M388" t="inlineStr">
         <is>
-          <t>Nhiệm vụ của tôi là thanh tẩy những Tapes of Last Words bằng bộ thanh tẩy tích hợp trong cơ thể và chứng minh rằng người đã khuất từng tồn tại.</t>
+          <t>Nhiệm vụ của ta là thanh tẩy những Cuộn Băng Lời Cuối bằng máy thanh tẩy tích hợp trong cơ thể, và chứng minh rằng những người đã khuất từng tồn tại.</t>
         </is>
       </c>
     </row>
@@ -25823,7 +25823,7 @@
       </c>
       <c r="M389" t="inlineStr">
         <is>
-          <t>Những người đã khám phá vì mọi người không đáng bị lạc trong cơn bão.</t>
+          <t>Những người đã dấn thân vì mọi người không đáng bị lạc mất trong cơn bão.</t>
         </is>
       </c>
     </row>
@@ -25888,7 +25888,7 @@
       </c>
       <c r="M390" t="inlineStr">
         <is>
-          <t>Nếu gặp bất kỳ Băng Cuối Cùng nào trong hành trình, hãy mang về cho tôi. Tôi sẽ thanh tẩy chúng và khắc ghi sự tồn tại của chúng trong tim.</t>
+          <t>Nếu trên đường đi gặp băng ghi Lời Cuối Cùng, cậu có thể mang đến cho tôi. Tôi sẽ thanh tẩy chúng và khắc ghi sự tồn tại của họ trong tim.</t>
         </is>
       </c>
     </row>
@@ -25953,7 +25953,7 @@
       </c>
       <c r="M391" t="inlineStr">
         <is>
-          <t>Sao không tự mình tìm kiếm họ?</t>
+          <t>Sao không tự mình đi tìm họ?</t>
         </is>
       </c>
     </row>
@@ -26018,7 +26018,7 @@
       </c>
       <c r="M392" t="inlineStr">
         <is>
-          <t>Chắc chắn rồi.</t>
+          <t>Được thôi.</t>
         </is>
       </c>
     </row>
@@ -26083,7 +26083,7 @@
       </c>
       <c r="M393" t="inlineStr">
         <is>
-          <t>Đừng lo, tình hình hiện tại vẫn nằm trong tính toán của tôi, và tôi vẫn có thể hoạt động được một thời gian.</t>
+          <t>Đừng lo, tình hình hiện tại vẫn nằm trong tính toán của ta, và ta vẫn có thể hoạt động được một thời gian nữa.</t>
         </is>
       </c>
     </row>
@@ -26148,7 +26148,7 @@
       </c>
       <c r="M394" t="inlineStr">
         <is>
-          <t>Ta rất cảm kích sự trợ giúp của ngươi. Mong ánh sáng của Reactor Drive luôn soi sáng chúng ta.</t>
+          <t>Cảm ơn sự trợ giúp của cậu. Mong ánh sáng của Reactor Drive luôn soi sáng chúng ta.</t>
         </is>
       </c>
     </row>
@@ -26213,7 +26213,7 @@
       </c>
       <c r="M395" t="inlineStr">
         <is>
-          <t>Nhiệm vụ của tôi là loại bỏ sự tha hóa khỏi Tape of Last Words và khôi phục những thông điệp chưa kịp nói của những người đã mất.</t>
+          <t>Xóa bỏ sự tha hóa trong Tape of Last Words và khôi phục những thông điệp chưa kịp cất lời của những người đã mất—đó là sứ mệnh của ta.</t>
         </is>
       </c>
     </row>
@@ -26343,7 +26343,7 @@
       </c>
       <c r="M397" t="inlineStr">
         <is>
-          <t>Đừng lo, thân thể ta sẽ trụ vững cho đến khi nhiệm vụ... đi đến hồi kết.</t>
+          <t>Đừng lo, thân xác ta sẽ trụ vững cho đến khi nhiệm vụ... hoàn thành.</t>
         </is>
       </c>
     </row>
@@ -26408,7 +26408,7 @@
       </c>
       <c r="M398" t="inlineStr">
         <is>
-          <t>Rover, có thời gian không?</t>
+          <t>Rover, cậu có thời gian không?</t>
         </is>
       </c>
     </row>
@@ -26473,7 +26473,7 @@
       </c>
       <c r="M399" t="inlineStr">
         <is>
-          <t>Bạn có muốn tham gia dự án nghiên cứu mới nhất của chúng tôi không?</t>
+          <t>Cậu có muốn tham gia dự án nghiên cứu mới nhất của chúng tôi không?</t>
         </is>
       </c>
     </row>
@@ -26538,7 +26538,7 @@
       </c>
       <c r="M400" t="inlineStr">
         <is>
-          <t>Yes.</t>
+          <t>Đúng vậy.</t>
         </is>
       </c>
     </row>
@@ -26668,7 +26668,7 @@
       </c>
       <c r="M402" t="inlineStr">
         <is>
-          <t>Tốt lắm. Để tôi giới thiệu nghiên cứu của chúng ta.</t>
+          <t>Tuyệt. Để tôi giới thiệu nghiên cứu của chúng ta.</t>
         </is>
       </c>
     </row>
@@ -26733,7 +26733,7 @@
       </c>
       <c r="M403" t="inlineStr">
         <is>
-          <t>Xin hãy cho chúng tôi một cơ hội. Trước tiên, tôi có thể giải thích về dự án.</t>
+          <t>Làm ơn, hãy cho chúng tôi một cơ hội. Trước hết, tôi sẽ giải thích dự án này là gì.</t>
         </is>
       </c>
     </row>
@@ -26798,7 +26798,7 @@
       </c>
       <c r="M404" t="inlineStr">
         <is>
-          <t>Bạn đã đến khu huấn luyện mô phỏng của Hướng Dẫn Viên Yhan chưa?</t>
+          <t>Cậu đã đến khu huấn luyện mô phỏng của Hướng Dẫn Viên Yhan chưa?</t>
         </is>
       </c>
     </row>
@@ -26863,7 +26863,7 @@
       </c>
       <c r="M405" t="inlineStr">
         <is>
-          <t>Người hướng dẫn Yhan sẽ sắp xếp các buổi mô phỏng để binh lính luyện tập chống lại ảnh toàn ký của kẻ địch và nâng cao kỹ năng chiến đấu.</t>
+          <t>Huấn luyện viên Yhan thường tổ chức các buổi mô phỏng để binh lính luyện tập chống lại hình ảnh toàn ký của kẻ địch và nâng cao kỹ năng chiến đấu.</t>
         </is>
       </c>
     </row>
@@ -26928,7 +26928,7 @@
       </c>
       <c r="M406" t="inlineStr">
         <is>
-          <t>Gần đây, chúng tôi đã phát triển công nghệ "hình chiếu" cải tiến để mô phỏng những kẻ địch mạnh hơn.</t>
+          <t>Gần đây, chúng tôi đã phát triển công nghệ "hình chiếu" cải tiến, có thể mô phỏng cả những kẻ địch mạnh hơn nữa.</t>
         </is>
       </c>
     </row>
@@ -26993,7 +26993,7 @@
       </c>
       <c r="M407" t="inlineStr">
         <is>
-          <t>Với công nghệ này, chúng ta có thể cung cấp chương trình huấn luyện toàn diện hơn cho binh lính. Điều này đồng nghĩa với kết quả tốt hơn cho mọi nhu cầu của họ.</t>
+          <t>Với công nghệ này, chúng ta có thể đào tạo binh lính toàn diện hơn. Điều đó đồng nghĩa với việc đáp ứng tốt hơn mọi nhu cầu của họ.</t>
         </is>
       </c>
     </row>
@@ -27058,7 +27058,7 @@
       </c>
       <c r="M408" t="inlineStr">
         <is>
-          <t>Chúng ta vẫn đang trong giai đoạn phát triển ban đầu, nên vẫn còn một số chi tiết kỹ thuật cần hoàn thiện.</t>
+          <t>Dự án vẫn còn ở giai đoạn đầu, nên còn vài chi tiết kỹ thuật cần hoàn thiện.</t>
         </is>
       </c>
     </row>
@@ -27123,7 +27123,7 @@
       </c>
       <c r="M409" t="inlineStr">
         <is>
-          <t>Bạn có sẵn lòng thử nghiệm cho chúng tôi và hỗ trợ nghiên cứu không?</t>
+          <t>Cậu có sẵn lòng thử nghiệm nó cho chúng tớ và giúp đỡ nghiên cứu không?</t>
         </is>
       </c>
     </row>
@@ -27188,7 +27188,7 @@
       </c>
       <c r="M410" t="inlineStr">
         <is>
-          <t>Chắc chắn rồi.</t>
+          <t>Được thôi.</t>
         </is>
       </c>
     </row>
@@ -27253,7 +27253,7 @@
       </c>
       <c r="M411" t="inlineStr">
         <is>
-          <t>Có gì cho tôi không?</t>
+          <t>Giúp thì được gì chứ?</t>
         </is>
       </c>
     </row>
@@ -27318,7 +27318,7 @@
       </c>
       <c r="M412" t="inlineStr">
         <is>
-          <t>Tôi biết cậu là người phù hợp để nói chuyện. Tôi đã gửi tọa độ cho cậu rồi. Cảm ơn đã giúp đỡ!</t>
+          <t>Tao biết cậu là người phù hợp để nói chuyện. Tao đã gửi tọa độ cho cậu rồi. Cảm ơn sự giúp đỡ của cậu!</t>
         </is>
       </c>
     </row>
@@ -27383,7 +27383,7 @@
       </c>
       <c r="M413" t="inlineStr">
         <is>
-          <t>Bạn sẽ biết khi đến đó. Tin tôi đi, nó sẽ đáng thời gian của bạn.</t>
+          <t>Đến nơi rồi cậu sẽ hiểu. Tin tôi đi, đáng để cậu bỏ thời gian đấy.</t>
         </is>
       </c>
     </row>
@@ -27448,7 +27448,7 @@
       </c>
       <c r="M414" t="inlineStr">
         <is>
-          <t>Nhiệt độ thuận lợi. Độ ẩm thì...</t>
+          <t>Điều kiện nhiệt độ thuận lợi. Độ ẩm thì...</t>
         </is>
       </c>
     </row>
@@ -27578,7 +27578,7 @@
       </c>
       <c r="M416" t="inlineStr">
         <is>
-          <t>Oh, it's you. Cậu đã thử nghiệm công nghệ mới nhất của chúng tôi chưa?</t>
+          <t>Ồ, là cậu à. Đã thử nghiệm công nghệ mới nhất của chúng ta chưa?</t>
         </is>
       </c>
     </row>
@@ -27643,7 +27643,7 @@
       </c>
       <c r="M417" t="inlineStr">
         <is>
-          <t>Vâng, tôi có.</t>
+          <t>Ừ, ta có.</t>
         </is>
       </c>
     </row>
@@ -27708,7 +27708,7 @@
       </c>
       <c r="M418" t="inlineStr">
         <is>
-          <t>Chưa xong.</t>
+          <t>Chưa.</t>
         </is>
       </c>
     </row>
@@ -27773,7 +27773,7 @@
       </c>
       <c r="M419" t="inlineStr">
         <is>
-          <t>Với sự trợ giúp của bạn, tôi tin rằng công nghệ của chúng ta sẽ sớm đạt đến tiềm năng tối đa để binh lính có thể sử dụng.</t>
+          <t>Nhờ sự hỗ trợ của cậu, ta tin rằng công nghệ của chúng ta sẽ sớm đạt đến tiềm năng tối đa để binh lính có thể sử dụng.</t>
         </is>
       </c>
     </row>
@@ -27838,7 +27838,7 @@
       </c>
       <c r="M420" t="inlineStr">
         <is>
-          <t>Nhớ ghé xem khi nào rảnh nhé! Tôi đã đăng ký giúp cậu rồi.</t>
+          <t>Nhớ lúc nào rảnh thì ghé qua xem thử đi! Tao đã đăng ký sẵn cho mày rồi đấy.</t>
         </is>
       </c>
     </row>
@@ -27903,7 +27903,7 @@
       </c>
       <c r="M421" t="inlineStr">
         <is>
-          <t>Vẻ mặt cậu cho thấy cậu có gì muốn hỏi.</t>
+          <t>Vẻ mặt của ngươi cho ta biết ngươi có điều muốn hỏi.</t>
         </is>
       </c>
     </row>
@@ -27968,7 +27968,7 @@
       </c>
       <c r="M422" t="inlineStr">
         <is>
-          <t>Làm thế nào bạn biết về dự án nghiên cứu này?</t>
+          <t>Làm sao cậu biết về dự án nghiên cứu này?</t>
         </is>
       </c>
     </row>
@@ -28033,7 +28033,7 @@
       </c>
       <c r="M423" t="inlineStr">
         <is>
-          <t>Cậu thực sự là nhà nghiên cứu à?</t>
+          <t>Ngươi thực sự là nhà nghiên cứu à?</t>
         </is>
       </c>
     </row>
@@ -28163,7 +28163,7 @@
       </c>
       <c r="M425" t="inlineStr">
         <is>
-          <t>Đôi mắt tinh tường. Đúng như ta mong đợi.</t>
+          <t>Đôi mắt cậu còn tinh tường hơn ta tưởng. Nhìn thấu được bản chất bên trong.</t>
         </is>
       </c>
     </row>
@@ -28228,7 +28228,7 @@
       </c>
       <c r="M426" t="inlineStr">
         <is>
-          <t>Xin lỗi, nhưng tôi chưa thể nói cho bạn biết lúc này. Chưa được đâu.</t>
+          <t>Xin lỗi, nhưng tôi chưa thể nói cho anh biết bây giờ. Chưa được đâu.</t>
         </is>
       </c>
     </row>
@@ -28293,7 +28293,7 @@
       </c>
       <c r="M427" t="inlineStr">
         <is>
-          <t>Đó là điều tôi chưa thể nói với cậu lúc này.</t>
+          <t>Đó là điều ta chưa thể nói cho ngươi biết lúc này.</t>
         </is>
       </c>
     </row>
@@ -28358,7 +28358,7 @@
       </c>
       <c r="M428" t="inlineStr">
         <is>
-          <t>Đôi mắt tinh tường. Đúng như ta mong đợi.</t>
+          <t>Đôi mắt cậu còn tinh tường hơn ta tưởng. Nhìn thấu được bản chất bên trong.</t>
         </is>
       </c>
     </row>
@@ -28423,7 +28423,7 @@
       </c>
       <c r="M429" t="inlineStr">
         <is>
-          <t>Xin lỗi, nhưng tôi chưa thể nói cho bạn biết lúc này. Chưa được đâu.</t>
+          <t>Xin lỗi, nhưng tôi chưa thể nói cho anh biết bây giờ. Chưa được đâu.</t>
         </is>
       </c>
     </row>
@@ -28488,7 +28488,7 @@
       </c>
       <c r="M430" t="inlineStr">
         <is>
-          <t>Nhân tiện, tôi có một việc nhỏ muốn nhờ. Cậu có thể giữ kín chuyện tôi liên quan đến Học Viện không?</t>
+          <t>À này, tôi có một việc nhỏ muốn nhờ. Cậu có thể giữ kín chuyện tôi liên quan đến Học viện không?</t>
         </is>
       </c>
     </row>
@@ -28553,7 +28553,7 @@
       </c>
       <c r="M431" t="inlineStr">
         <is>
-          <t>Cảm ơn, Rover.</t>
+          <t>Cảm ơn cậu, Rover.</t>
         </is>
       </c>
     </row>
@@ -28618,7 +28618,7 @@
       </c>
       <c r="M432" t="inlineStr">
         <is>
-          <t>Đây chắc là thứ hình chiếu mà Qinggong nói đến... Tớ nên thử xem sao.</t>
+          <t>Đây chắc là cái thiết bị chiếu mà Qinggong nói... Ta nên thử xem sao.</t>
         </is>
       </c>
     </row>
@@ -28683,7 +28683,7 @@
       </c>
       <c r="M433" t="inlineStr">
         <is>
-          <t>Hello, {PlayerName}. Cậu có nghe thấy tôi không...? Tôi là Người Canh Cổng Hắc Ám.</t>
+          <t>Chào {PlayerName}. Cậu có nghe thấy ta không...? Ta là Người Canh Gác Cổng Ebony đây.</t>
         </is>
       </c>
     </row>
@@ -28748,7 +28748,7 @@
       </c>
       <c r="M434" t="inlineStr">
         <is>
-          <t>Sao cơ?</t>
+          <t>Lại đến nữa à?</t>
         </is>
       </c>
     </row>
@@ -28813,7 +28813,7 @@
       </c>
       <c r="M435" t="inlineStr">
         <is>
-          <t>Sao cậu gọi tôi?</t>
+          <t>Sao gọi tao?</t>
         </is>
       </c>
     </row>
@@ -28878,7 +28878,7 @@
       </c>
       <c r="M436" t="inlineStr">
         <is>
-          <t>Hello, tôi là Gatekeeper Ngà.</t>
+          <t>Xin chào, tôi là Người Gác Cổng Ngà.</t>
         </is>
       </c>
     </row>
@@ -28943,7 +28943,7 @@
       </c>
       <c r="M437" t="inlineStr">
         <is>
-          <t>Hừm. Ta là Người Quản lý của &lt;ano=domain of dreams&gt;Somnoire&lt;/ano&gt;, Ebony Gatekeeper.</t>
+          <t>Ờ hựm. Ta là Người Quản lý của &lt;ano=domain of dreams&gt;Somnoire&lt;/ano&gt;, Người Gác Cổng Hắc Ám.</t>
         </is>
       </c>
     </row>
@@ -29008,7 +29008,7 @@
       </c>
       <c r="M438" t="inlineStr">
         <is>
-          <t>Ừm... để gặp anh về chuyện liên quan đến Somnoire thôi mà.</t>
+          <t>Ừm... để gặp cậu về chuyện liên quan đến Somnoire thôi mà.</t>
         </is>
       </c>
     </row>
@@ -29073,7 +29073,7 @@
       </c>
       <c r="M439" t="inlineStr">
         <is>
-          <t>Hừm. Có lẽ nên để trò đùa đó lại sau, Dreamwalker.</t>
+          <t>Ờ hừm... Để dành trò đùa đó sau đi, Dreamwalker.</t>
         </is>
       </c>
     </row>
@@ -29138,7 +29138,7 @@
       </c>
       <c r="M440" t="inlineStr">
         <is>
-          <t>Ta đang tự hỏi liệu ngươi có nhận thấy không... Một cánh cổng dẫn đến Somnoire đã bắt đầu xuất hiện ở Rinascita.</t>
+          <t>Tao đang thắc mắc liệu cậu có để ý không... Một cánh cổng dẫn đến Somnoire đã bắt đầu xuất hiện ở Rinascita.</t>
         </is>
       </c>
     </row>
@@ -29203,7 +29203,7 @@
       </c>
       <c r="M441" t="inlineStr">
         <is>
-          <t>(Giọng bị nghẹt)</t>
+          <t>(Giọng nghẹn ngào)</t>
         </is>
       </c>
     </row>
@@ -29268,7 +29268,7 @@
       </c>
       <c r="M442" t="inlineStr">
         <is>
-          <t>Hello?</t>
+          <t>Xin chào?</t>
         </is>
       </c>
     </row>
@@ -29333,7 +29333,7 @@
       </c>
       <c r="M443" t="inlineStr">
         <is>
-          <t>Tín hiệu bị ngắt quãng.</t>
+          <t>Tín hiệu đang bị nhiễu.</t>
         </is>
       </c>
     </row>
@@ -29398,7 +29398,7 @@
       </c>
       <c r="M444" t="inlineStr">
         <is>
-          <t>Khung cảnh mộng mị dường như đang gặp phải một số nhiễu loạn... À, đã hoạt động lại rồi.</t>
+          <t>Giấc mộng hình như đang gặp phải nhiễu loạn... À, đã ổn lại rồi.</t>
         </is>
       </c>
     </row>
@@ -29463,7 +29463,7 @@
       </c>
       <c r="M445" t="inlineStr">
         <is>
-          <t>Nếu có thể, tôi muốn nói chuyện trực tiếp với bạn. Tôi sẽ đợi bạn, Dreamwalker.</t>
+          <t>Nếu có thể, ta muốn nói chuyện trực tiếp với ngươi. Ta sẽ đợi ngươi đấy, Dreamwalker.</t>
         </is>
       </c>
     </row>
@@ -29528,7 +29528,7 @@
       </c>
       <c r="M446" t="inlineStr">
         <is>
-          <t>À. {PlayerName}. Cậu đã đến rồi.</t>
+          <t>À... {PlayerName}. Cậu đã đến rồi.</t>
         </is>
       </c>
     </row>
@@ -29593,7 +29593,7 @@
       </c>
       <c r="M447" t="inlineStr">
         <is>
-          <t>Ừm... Tôi đoán chắc bạn đang bối rối trước diện mạo hiện tại của tôi. Tôi có thể đảm bảo với bạn rằng tôi chính là Ebony Gatekeeper đã liên lạc với bạn trước đó.</t>
+          <t>Ừm... Chắc hẳn cậu đang thắc mắc về ngoại hình hiện tại của ta. Ta có thể đảm bảo với cậu, ta chính là Người Gác Cổng Hắc Ám đã liên lạc với cậu trước đó.</t>
         </is>
       </c>
     </row>
@@ -29658,7 +29658,7 @@
       </c>
       <c r="M448" t="inlineStr">
         <is>
-          <t>Bạn đang ở bên trong Cosmos của Encore?</t>
+          <t>Cậu đang ở bên trong Vũ trụ Encore à?</t>
         </is>
       </c>
     </row>
@@ -29723,7 +29723,7 @@
       </c>
       <c r="M449" t="inlineStr">
         <is>
-          <t>...Ra là vậy. Chính cậu là người tôi đã nói chuyện lần trước!</t>
+          <t>...Ra là vậy. Chính cậu là người tôi đã nói chuyện lần đó!</t>
         </is>
       </c>
     </row>
@@ -29788,7 +29788,7 @@
       </c>
       <c r="M450" t="inlineStr">
         <is>
-          <t>Okay..</t>
+          <t>Ừm...</t>
         </is>
       </c>
     </row>
@@ -29853,7 +29853,7 @@
       </c>
       <c r="M451" t="inlineStr">
         <is>
-          <t>Thôi nào. Điều này không liên quan đến chủ đề chúng ta sắp thảo luận.</t>
+          <t>Vậy thì, đây không liên quan đến chủ đề chúng ta sắp thảo luận đâu.</t>
         </is>
       </c>
     </row>
@@ -29918,7 +29918,7 @@
       </c>
       <c r="M452" t="inlineStr">
         <is>
-          <t>Lần đó... lần đó ấy à?</t>
+          <t>Lần đó... lần đó sao?</t>
         </is>
       </c>
     </row>
@@ -29983,7 +29983,7 @@
       </c>
       <c r="M453" t="inlineStr">
         <is>
-          <t>Lần đó khi tôi dùng Echoid chống lại bọn TD.</t>
+          <t>Lần đó khi ta dùng Echoid chống lại bọn TD.</t>
         </is>
       </c>
     </row>
@@ -30048,7 +30048,7 @@
       </c>
       <c r="M454" t="inlineStr">
         <is>
-          <t>Ờ... À... Đúng vậy, cậu nói hoàn toàn chính xác. Chính tôi là người mà cậu đã nói chuyện.</t>
+          <t>Ờ hừm... À... Đúng vậy, cậu nói không sai. Chính ta là người cậu đã nói chuyện cùng.</t>
         </is>
       </c>
     </row>
@@ -30113,7 +30113,7 @@
       </c>
       <c r="M455" t="inlineStr">
         <is>
-          <t>Thôi nói đi. Lần này ngươi định làm gì?</t>
+          <t>Nói đi, lần này mày định giở trò gì?</t>
         </is>
       </c>
     </row>
@@ -30178,7 +30178,7 @@
       </c>
       <c r="M456" t="inlineStr">
         <is>
-          <t>Xin hãy tin tôi, Dreamwalker. Tôi đảm bảo rằng mình không có bí mật gì để giấu giếm.</t>
+          <t>Xin hãy tin tôi, Dreamwalker. Tôi không có bí mật gì để che giấu cả.</t>
         </is>
       </c>
     </row>
@@ -30243,7 +30243,7 @@
       </c>
       <c r="M457" t="inlineStr">
         <is>
-          <t>Những tạp chất này là gì?</t>
+          <t>Những tạp chất này là gì thế?</t>
         </is>
       </c>
     </row>
@@ -30308,7 +30308,7 @@
       </c>
       <c r="M458" t="inlineStr">
         <is>
-          <t>Dreamwalker, ta muốn nhờ ngươi giúp xử lý những tạp chất này. Nhưng không phải vì ta, mà vì toàn bộ Somnoire.</t>
+          <t>Người Du Hành Giấc Mơ à, ta muốn nhờ ngươi xử lý những tạp chất này. Nhưng không phải vì ta, mà vì toàn bộ Somnoire.</t>
         </is>
       </c>
     </row>
@@ -30373,7 +30373,7 @@
       </c>
       <c r="M459" t="inlineStr">
         <is>
-          <t>Được thôi. Không phải lần đầu tôi làm chuyện này.</t>
+          <t>Được thôi. Chẳng phải lần đầu ta làm chuyện này.</t>
         </is>
       </c>
     </row>
@@ -30503,7 +30503,7 @@
       </c>
       <c r="M461" t="inlineStr">
         <is>
-          <t>Yên tâm đi, sẽ có rất nhiều phần thưởng đang chờ bạn trong những giấc mộng. Tôi cũng sẽ sẵn sàng hỗ trợ bạn bằng mọi khả năng của mình.</t>
+          <t>Yên tâm đi, bên trong thế giới mộng ảo sẽ có rất nhiều phần thưởng đang chờ cậu. Tôi cũng sẽ hỗ trợ cậu hết khả năng có thể.</t>
         </is>
       </c>
     </row>
@@ -30568,7 +30568,7 @@
       </c>
       <c r="M462" t="inlineStr">
         <is>
-          <t>Tiến đến cổng kết nối và khôi phục các Vùng Ký Ức bị tạp chất xâm nhập, Dreamwalker.</t>
+          <t>Đến cổng kết nối và khôi phục các Khu Vực Ký Ức bị ô nhiễm, Hành Giả Giấc Mơ</t>
         </is>
       </c>
     </row>
@@ -30633,7 +30633,7 @@
       </c>
       <c r="M463" t="inlineStr">
         <is>
-          <t>Lần gặp "Dorothy" ấy...</t>
+          <t>Lần đó khi ta gặp "Dorothy"...</t>
         </is>
       </c>
     </row>
@@ -30698,7 +30698,7 @@
       </c>
       <c r="M464" t="inlineStr">
         <is>
-          <t>Dreamwalker à, với Somnoire, ngươi là một biến số có sức nặng không tưởng. Ngươi mang đến sự thay đổi...</t>
+          <t>Dreamwalker, với Somnoire, cậu là một biến số vô cùng quan trọng. Cậu mang đến sự thay đổi...</t>
         </is>
       </c>
     </row>
@@ -30828,7 +30828,7 @@
       </c>
       <c r="M466" t="inlineStr">
         <is>
-          <t>Một sự thay đổi tốt đẹp. Sau nhiều năm nằm im, người khổng lồ giờ đây đang trải qua sự biến đổi. Cùng nhau, chúng ta sẽ bảo vệ thêm nhiều... kho báu hơn nữa.</t>
+          <t>Một sự thay đổi tốt đẹp. Sau bao năm nằm im, người khổng lồ giờ đây đang trải qua sự biến đổi. Cùng nhau, chúng ta sẽ bảo vệ được nhiều... kho báu hơn nữa.</t>
         </is>
       </c>
     </row>
@@ -30893,7 +30893,7 @@
       </c>
       <c r="M467" t="inlineStr">
         <is>
-          <t>Khi ở sâu bên trong Memory Zones, chắc hẳn bạn đã bắt gặp rất nhiều &lt;b&gt;cảnh vật và sự kiện quen thuộc&lt;/b&gt;.</t>
+          <t>Khi lặn sâu vào các Memory Zones, chắc hẳn cậu đã bắt gặp không ít &lt;b&gt;cảnh vật và sự kiện quen thuộc&lt;/b&gt; rồi nhỉ.</t>
         </is>
       </c>
     </row>
@@ -30958,7 +30958,7 @@
       </c>
       <c r="M468" t="inlineStr">
         <is>
-          <t>Hãy đi, Dreamwalker. Trong cõi mộng, chỉ có giấc mơ mới nắm giữ câu trả lời chúng ta tìm kiếm.</t>
+          <t>Đi đi, Kẻ lang thang trong Giấc mơ. Trong cõi mộng, chỉ có giấc mơ mới nắm giữ câu trả lời ta tìm kiếm.</t>
         </is>
       </c>
     </row>
@@ -31023,7 +31023,7 @@
       </c>
       <c r="M469" t="inlineStr">
         <is>
-          <t>Bạn đây rồi! Đúng giờ luôn, {PlayerName}.</t>
+          <t>Cậu đây rồi! Đúng giờ quá, {PlayerName}.</t>
         </is>
       </c>
     </row>
@@ -31088,7 +31088,7 @@
       </c>
       <c r="M470" t="inlineStr">
         <is>
-          <t>Chuyện gì đã xảy ra?</t>
+          <t>Chuyện gì đã xảy ra thế?</t>
         </is>
       </c>
     </row>
@@ -31218,7 +31218,7 @@
       </c>
       <c r="M472" t="inlineStr">
         <is>
-          <t>Đừng lo. Hiện chưa có tình huống khẩn cấp nào cần cậu xử lý… ít nhất là chưa có.</t>
+          <t>Đừng lo. Hiện tại chưa có tình huống khẩn cấp nào cần cậu phải lo lắng… ít nhất là chưa.</t>
         </is>
       </c>
     </row>
@@ -31283,7 +31283,7 @@
       </c>
       <c r="M473" t="inlineStr">
         <is>
-          <t>Lần này, đó là một lời mời mà chúng ta không ngờ tới.</t>
+          <t>Lần này, đó là lời mời mà chúng ta không ngờ tới.</t>
         </is>
       </c>
     </row>
@@ -31348,7 +31348,7 @@
       </c>
       <c r="M474" t="inlineStr">
         <is>
-          <t>Người gác cổng Ngà trao cho bạn một tấm thiệp được chế tác tinh xảo. Khi nhìn dòng chữ viết tay xa lạ, cụm từ "Solaris Film Festival" hiện ra nổi bật.</t>
+          <t>Người Gác Cổng Ngà trao cho cậu một tấm thiệp được chế tác tinh xảo. Khi lướt mắt qua những dòng chữ viết tay xa lạ, dòng chữ "Liên hoan Phim Solaris" hiện ra nổi bật.</t>
         </is>
       </c>
     </row>
@@ -31413,7 +31413,7 @@
       </c>
       <c r="M475" t="inlineStr">
         <is>
-          <t>Cái gì đây?</t>
+          <t>Đây là cái gì?</t>
         </is>
       </c>
     </row>
@@ -31478,7 +31478,7 @@
       </c>
       <c r="M476" t="inlineStr">
         <is>
-          <t>Hai người đã sắp xếp chuyện này à?</t>
+          <t>Hai người bày trò này à?</t>
         </is>
       </c>
     </row>
@@ -31738,7 +31738,7 @@
       </c>
       <c r="M480" t="inlineStr">
         <is>
-          <t>Và giờ đây, họ đã gửi lời mời. Có lẽ con đường dẫn đến những tầng sâu hơn của Somnoire cuối cùng đã mở ra.</t>
+          <t>Và giờ đây, họ đã gửi lời mời. Có lẽ con đường dẫn vào tầng sâu hơn của Somnoire cuối cùng đã mở ra.</t>
         </is>
       </c>
     </row>
@@ -31803,7 +31803,7 @@
       </c>
       <c r="M481" t="inlineStr">
         <is>
-          <t>Nghe có vẻ rắc rối đấy.</t>
+          <t>Nghe có vẻ rắc rối rồi.</t>
         </is>
       </c>
     </row>
@@ -31868,7 +31868,7 @@
       </c>
       <c r="M482" t="inlineStr">
         <is>
-          <t>Hay… có khi chỉ là một lễ hội phim mới thôi?</t>
+          <t>Hay là... chỉ là một lễ hội phim mới thôi?</t>
         </is>
       </c>
     </row>
@@ -31933,7 +31933,7 @@
       </c>
       <c r="M483" t="inlineStr">
         <is>
-          <t>Đúng vậy. Dù chúng ta chưa thể xác định được ý định thực sự của chủ nhân, nhưng có một điều chắc chắn: cả hai chúng ta, những Gatekeeper, đều không thể tiếp cận các tầng sâu hơn. Chỉ có bạn mới làm được.</t>
+          <t>Đúng thế. Dù ta chưa thể xác định được ý định thực sự của chủ thể, nhưng có một điều chắc chắn: cả hai chúng ta, những Người Gác Cổng, đều không thể tiếp cận các tầng sâu hơn. Chỉ có mình cậu mới làm được.</t>
         </is>
       </c>
     </row>
@@ -31998,7 +31998,7 @@
       </c>
       <c r="M484" t="inlineStr">
         <is>
-          <t>Nhưng cả hai chúng tôi, những Gatekeeper, đều không thể tiếp cận các tầng sâu hơn. Chỉ có bạn mới làm được.</t>
+          <t>Nhưng cả hai chúng ta, những Người Gác Cổng, đều không thể tiếp cận những tầng sâu hơn. Chỉ có cậu mới làm được.</t>
         </is>
       </c>
     </row>
@@ -32063,7 +32063,7 @@
       </c>
       <c r="M485" t="inlineStr">
         <is>
-          <t>Nói cách khác, lời mời này chỉ dành riêng cho cậu thôi.</t>
+          <t>Nói cách khác, lời mời này chỉ dành riêng cho cậu mà thôi.</t>
         </is>
       </c>
     </row>
@@ -32193,7 +32193,7 @@
       </c>
       <c r="M487" t="inlineStr">
         <is>
-          <t>Có vẻ như tôi không còn lựa chọn nào khác.</t>
+          <t>Có vẻ là ta không còn lựa chọn nào khác.</t>
         </is>
       </c>
     </row>
@@ -32258,7 +32258,7 @@
       </c>
       <c r="M488" t="inlineStr">
         <is>
-          <t>Nếu nơi đó an toàn, hãy tận hưởng lễ hội nhé. Chúng tôi sẽ đợi cậu trở về.</t>
+          <t>Nếu nơi đó thực sự an toàn, hãy tận hưởng lễ hội nhé. Chúng tôi sẽ đợi cậu trở về.</t>
         </is>
       </c>
     </row>
@@ -32323,7 +32323,7 @@
       </c>
       <c r="M489" t="inlineStr">
         <is>
-          <t>Hiệp sĩ của ta… đã ngã hết rồi sao?</t>
+          <t>Các hiệp sĩ của ta… tất cả đều đã ngã xuống sao?</t>
         </is>
       </c>
     </row>
@@ -32388,7 +32388,7 @@
       </c>
       <c r="M490" t="inlineStr">
         <is>
-          <t>Vậy thì gánh nặng cuối cùng chỉ còn mình ta gánh vác.</t>
+          <t>Vậy thì trách nhiệm cuối cùng chỉ còn lại mình ta mà thôi.</t>
         </is>
       </c>
     </row>
@@ -32453,7 +32453,7 @@
       </c>
       <c r="M491" t="inlineStr">
         <is>
-          <t>(*Cái quái gì thế này...? Thôi kệ, cứ tạm chiều theo vậy.*)</t>
+          <t>("Chuyện quái quỷ gì thế này... Thôi kệ, cứ chơi theo ván bài của họ đã.")</t>
         </is>
       </c>
     </row>
@@ -32518,7 +32518,7 @@
       </c>
       <c r="M492" t="inlineStr">
         <is>
-          <t>À, vậy chắc hẳn cậu là {PlayerName}? Name của cậu đã vang xa rồi. Những câu chuyện về cậu đã theo gió và tần số đến tai tôi từ lâu lắm rồi.</t>
+          <t>À, vậy ra cậu chính là {PlayerName}? Tên tuổi của cậu đã đến tai ta từ lâu. Những chiến công của cậu đã theo gió và tần số mà truyền đến đây.</t>
         </is>
       </c>
     </row>
@@ -32583,7 +32583,7 @@
       </c>
       <c r="M493" t="inlineStr">
         <is>
-          <t>Ta là Grand Commander, thủ lĩnh của Hiệp sĩ Hoang Dã.</t>
+          <t>Ta là Tổng Tư Lệnh, thủ lĩnh của các Hiệp Sĩ Hoang Dã.</t>
         </is>
       </c>
     </row>
@@ -32648,7 +32648,7 @@
       </c>
       <c r="M494" t="inlineStr">
         <is>
-          <t>Ta cứ tưởng hiệp sĩ chỉ có ở Rinascita thôi.</t>
+          <t>Tớ tưởng các hiệp sĩ chỉ có trong Rinascita thôi cơ.</t>
         </is>
       </c>
     </row>
@@ -32713,7 +32713,7 @@
       </c>
       <c r="M495" t="inlineStr">
         <is>
-          <t>Ta là Grand Commander thứ 18 của Hiệp sĩ Hoang Dã. Hãy hỏi Astra hoặc Caldheim, cả hai sẽ chứng thực ý nghĩa và vinh quang của hội chúng ta.</t>
+          <t>Ta là Chỉ Huy Trưởng thứ 18 của Hiệp Sĩ Đoàn Hoang Dã. Hãy hỏi Astra hay Caldheim, cả hai đều có thể chứng thực cho ý nghĩa và vinh quang của đoàn ta.</t>
         </is>
       </c>
     </row>
@@ -32778,7 +32778,7 @@
       </c>
       <c r="M496" t="inlineStr">
         <is>
-          <t>Astra và Caldheim... Họ rốt cuộc là ai vậy nhỉ?</t>
+          <t>Astra và Caldheim... Họ rốt cuộc là ai vậy?</t>
         </is>
       </c>
     </row>
@@ -32973,7 +32973,7 @@
       </c>
       <c r="M499" t="inlineStr">
         <is>
-          <t>Còn có Petrahane, Airelas, Honya, Albin, Golesia, Stieler, Landry, Erthgold… Họ đã chiến đấu quá lâu rồi. Liệu ngươi có thật sự cứu được tất cả?</t>
+          <t>Còn có Petrahane, Airelas, Honya, Albin, Golesia, Stieler, Landry, Erthgold… Họ đã chiến đấu quá lâu rồi. Liệu cậu có thật sự cứu được tất cả không?</t>
         </is>
       </c>
     </row>
@@ -33038,7 +33038,7 @@
       </c>
       <c r="M500" t="inlineStr">
         <is>
-          <t>Gánh nặng giờ thuộc về tôi.</t>
+          <t>Gánh nặng này giờ đã đặt lên vai ta.</t>
         </is>
       </c>
     </row>
